--- a/financial_models/Macro_Monitor.xlsx
+++ b/financial_models/Macro_Monitor.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v3\financial_models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05346381-C95F-4789-85A7-C132F0D97176}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32A207E0-0677-468C-B427-147244F02532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="195">
   <si>
     <t>China</t>
   </si>
@@ -265,449 +265,457 @@
     <t>https://fred.stlouisfed.org/series/CPALTT01CNM659N</t>
   </si>
   <si>
+    <t>BBB Bond yield</t>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/china/government-bond-yield</t>
+  </si>
+  <si>
+    <t>https://iftp.chinamoney.com.cn/chinese/scsjzqxx/</t>
+  </si>
+  <si>
+    <t>https://yield.chinabond.com.cn/cbweb-mn/yield_main?locale=en_US</t>
+  </si>
+  <si>
+    <t>CN Onshore BBB- Bond yield</t>
+  </si>
+  <si>
+    <t>CN Offshore BBB- Bond yield</t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/series/DGS10</t>
+  </si>
+  <si>
+    <t>CN</t>
+  </si>
+  <si>
+    <t>Target Return</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Crude oil</t>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/commodity/crude-oil</t>
+  </si>
+  <si>
+    <t>Energy:</t>
+  </si>
+  <si>
+    <t>Gold</t>
+  </si>
+  <si>
+    <t>Metals:</t>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/commodity/gold</t>
+  </si>
+  <si>
+    <t>All-in-one Dash Board</t>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/commodities</t>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/commodity/wheat</t>
+  </si>
+  <si>
+    <t>Wheat</t>
+  </si>
+  <si>
+    <t>Agricultural:</t>
+  </si>
+  <si>
+    <t>All-in-one Currency Dashboard</t>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/currencies</t>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/china/currency</t>
+  </si>
+  <si>
+    <t>USDCNY</t>
+  </si>
+  <si>
+    <t>All-in-One Bond Prices</t>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/bonds</t>
+  </si>
+  <si>
+    <t>All-in-One Growth Rate</t>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/country-list/gdp-growth-rate</t>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/country-list/inflation-rate</t>
+  </si>
+  <si>
+    <t>All-in-One Inflation Rate</t>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/cadcny:cur</t>
+  </si>
+  <si>
+    <t>CADCNY</t>
+  </si>
+  <si>
+    <t>HKDCNY</t>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/hkdcny:cur</t>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/canada/currency</t>
+  </si>
+  <si>
+    <t>USDCAD</t>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/japan/currency</t>
+  </si>
+  <si>
+    <t>USDJAY</t>
+  </si>
+  <si>
+    <t>EURUSD</t>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/euro-area/currency</t>
+  </si>
+  <si>
+    <t>https://hk.centanet.com/CCI/CCI</t>
+  </si>
+  <si>
+    <t>Canada</t>
+  </si>
+  <si>
+    <t>USA</t>
+  </si>
+  <si>
+    <t>UK</t>
+  </si>
+  <si>
+    <t>Australia</t>
+  </si>
+  <si>
+    <t>Residential</t>
+  </si>
+  <si>
+    <t>Commercial</t>
+  </si>
+  <si>
+    <t>Logics - do not delete</t>
+  </si>
+  <si>
+    <t>Economic Indicators</t>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/china/forecast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. China </t>
+  </si>
+  <si>
+    <t>Non-Manufacturing PMI</t>
+  </si>
+  <si>
+    <t>Manufacturing PMI</t>
+  </si>
+  <si>
+    <t>1. US</t>
+  </si>
+  <si>
+    <t>GDP &amp; CPI</t>
+  </si>
+  <si>
+    <t>Balance of Payment</t>
+  </si>
+  <si>
+    <t>2. China</t>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/china/balance-of-trade</t>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/china/current-account</t>
+  </si>
+  <si>
+    <t>Current Account (CA)</t>
+  </si>
+  <si>
+    <t>Capital Account (KA)</t>
+  </si>
+  <si>
+    <t>Financial Account (RA)</t>
+  </si>
+  <si>
+    <t>Net Errors and Ommisions (EA)</t>
+  </si>
+  <si>
+    <t>Leading Indicators</t>
+  </si>
+  <si>
+    <t>https://www.conference-board.org/topics/global-economic-outlook</t>
+  </si>
+  <si>
+    <t>Global Outlook</t>
+  </si>
+  <si>
+    <t>1. US LEI</t>
+  </si>
+  <si>
+    <t>https://en.macromicro.me/collections/25/cn-industry-relative/232/cn-pmi-caixin</t>
+  </si>
+  <si>
+    <t>Non-Manufacturing NMI</t>
+  </si>
+  <si>
+    <t>https://en.macromicro.me/collections/25/cn-industry-relative/233/cn-nmi-caixin</t>
+  </si>
+  <si>
+    <t>2. Global LEI</t>
+  </si>
+  <si>
+    <t>https://www.conference-board.org/topics/business-cycle-indicators</t>
+  </si>
+  <si>
+    <t>https://www.conference-board.org/topics/us-leading-indicators</t>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/united-states/forecast</t>
+  </si>
+  <si>
+    <t>https://en.macromicro.me/collections/8/us-industry-relative/54/ism</t>
+  </si>
+  <si>
+    <t>https://en.macromicro.me/collections/8/us-industry-relative/55/ism-nonmanus</t>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/commodity/crb</t>
+  </si>
+  <si>
+    <t>CRB Commodity Index</t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/series/VIXCLS</t>
+  </si>
+  <si>
+    <t>Sentiment/Volatility</t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/series/CHNB6FATT01CXCUQ</t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/series/CHNB6FARA01CXCUQ</t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/series/CHNB6CATT00CXCUQ</t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/series/FEDFUNDS</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>US 10Y Treasury yield</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>US Fed Fund Rate</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>US BBB Bond index yield</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>CN 10Y Government Bond Yield</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/china/interest-rate</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>CN Loan Prime Rate</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/series/BAMLC0A2CAAEY</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>US AA Bond index yield</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.spglobal.com/spdji/en/indices/fixed-income/sp-china-corporate-bond-index/#overview</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>CN AA Bond index yield</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/commodity/coal</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Coal</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Natural </t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/commodity/natural-gas</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stock Indices</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>S&amp;P 500</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>3. Canada</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>DJI</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://finance.yahoo.com/quote/%5EDJI/</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://finance.yahoo.com/quote/%5EGSPC/</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Nikkei 225</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>4. Japan</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/canada/stock-market</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>TSX</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.etnet.com.hk/www/tc/stocks/indexes_chart_interactive.php?subtype=HIS</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.sgx.com/indices/products/sti</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>STI</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>5. Singapore</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/japan/stock-market</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/stocks</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/china/stock-market</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>6. Australia</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/australia/stock-market</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>ASX</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>7. India</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/india/stock-market</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sensex</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/united-kingdom/stock-market</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>8. Britain</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>FTSE 100</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shanghai Composite Index</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hang Seng Index</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/united-states/stock-market</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>ERP</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bond Premium</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equity Cost</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Nominal Rf rate</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
     <t>Market Yields:</t>
-  </si>
-  <si>
-    <t>Others</t>
-  </si>
-  <si>
-    <t>BBB Bond yield</t>
-  </si>
-  <si>
-    <t>Offshore BBB- Bond yield</t>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/china/government-bond-yield</t>
-  </si>
-  <si>
-    <t>https://iftp.chinamoney.com.cn/chinese/scsjzqxx/</t>
-  </si>
-  <si>
-    <t>https://yield.chinabond.com.cn/cbweb-mn/yield_main?locale=en_US</t>
-  </si>
-  <si>
-    <t>CN Onshore BBB- Bond yield</t>
-  </si>
-  <si>
-    <t>CN Offshore BBB- Bond yield</t>
-  </si>
-  <si>
-    <t>https://fred.stlouisfed.org/series/DGS10</t>
-  </si>
-  <si>
-    <t>CN</t>
-  </si>
-  <si>
-    <t>Target Return</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>Crude oil</t>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/commodity/crude-oil</t>
-  </si>
-  <si>
-    <t>Energy:</t>
-  </si>
-  <si>
-    <t>Gold</t>
-  </si>
-  <si>
-    <t>Metals:</t>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/commodity/gold</t>
-  </si>
-  <si>
-    <t>All-in-one Dash Board</t>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/commodities</t>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/commodity/wheat</t>
-  </si>
-  <si>
-    <t>Wheat</t>
-  </si>
-  <si>
-    <t>Agricultural:</t>
-  </si>
-  <si>
-    <t>All-in-one Currency Dashboard</t>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/currencies</t>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/china/currency</t>
-  </si>
-  <si>
-    <t>USDCNY</t>
-  </si>
-  <si>
-    <t>All-in-One Bond Prices</t>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/bonds</t>
-  </si>
-  <si>
-    <t>All-in-One Growth Rate</t>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/country-list/gdp-growth-rate</t>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/country-list/inflation-rate</t>
-  </si>
-  <si>
-    <t>All-in-One Inflation Rate</t>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/cadcny:cur</t>
-  </si>
-  <si>
-    <t>CADCNY</t>
-  </si>
-  <si>
-    <t>HKDCNY</t>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/hkdcny:cur</t>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/canada/currency</t>
-  </si>
-  <si>
-    <t>USDCAD</t>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/japan/currency</t>
-  </si>
-  <si>
-    <t>USDJAY</t>
-  </si>
-  <si>
-    <t>EURUSD</t>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/euro-area/currency</t>
-  </si>
-  <si>
-    <t>https://hk.centanet.com/CCI/CCI</t>
-  </si>
-  <si>
-    <t>Canada</t>
-  </si>
-  <si>
-    <t>USA</t>
-  </si>
-  <si>
-    <t>UK</t>
-  </si>
-  <si>
-    <t>Australia</t>
-  </si>
-  <si>
-    <t>Residential</t>
-  </si>
-  <si>
-    <t>Commercial</t>
-  </si>
-  <si>
-    <t>Discount Rate</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Notes</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>Forex</t>
-  </si>
-  <si>
-    <t>Logics - do not delete</t>
-  </si>
-  <si>
-    <t>Economic Indicators</t>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/china/forecast</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. China </t>
-  </si>
-  <si>
-    <t>Non-Manufacturing PMI</t>
-  </si>
-  <si>
-    <t>Manufacturing PMI</t>
-  </si>
-  <si>
-    <t>1. US</t>
-  </si>
-  <si>
-    <t>GDP &amp; CPI</t>
-  </si>
-  <si>
-    <t>Balance of Payment</t>
-  </si>
-  <si>
-    <t>2. China</t>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/china/balance-of-trade</t>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/china/current-account</t>
-  </si>
-  <si>
-    <t>Current Account (CA)</t>
-  </si>
-  <si>
-    <t>Capital Account (KA)</t>
-  </si>
-  <si>
-    <t>Financial Account (RA)</t>
-  </si>
-  <si>
-    <t>Net Errors and Ommisions (EA)</t>
-  </si>
-  <si>
-    <t>Leading Indicators</t>
-  </si>
-  <si>
-    <t>https://www.conference-board.org/topics/global-economic-outlook</t>
-  </si>
-  <si>
-    <t>Global Outlook</t>
-  </si>
-  <si>
-    <t>1. US LEI</t>
-  </si>
-  <si>
-    <t>https://en.macromicro.me/collections/25/cn-industry-relative/232/cn-pmi-caixin</t>
-  </si>
-  <si>
-    <t>Non-Manufacturing NMI</t>
-  </si>
-  <si>
-    <t>https://en.macromicro.me/collections/25/cn-industry-relative/233/cn-nmi-caixin</t>
-  </si>
-  <si>
-    <t>2. Global LEI</t>
-  </si>
-  <si>
-    <t>https://www.conference-board.org/topics/business-cycle-indicators</t>
-  </si>
-  <si>
-    <t>https://www.conference-board.org/topics/us-leading-indicators</t>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/united-states/forecast</t>
-  </si>
-  <si>
-    <t>https://en.macromicro.me/collections/8/us-industry-relative/54/ism</t>
-  </si>
-  <si>
-    <t>https://en.macromicro.me/collections/8/us-industry-relative/55/ism-nonmanus</t>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/commodity/crb</t>
-  </si>
-  <si>
-    <t>CRB Commodity Index</t>
-  </si>
-  <si>
-    <t>https://fred.stlouisfed.org/series/VIXCLS</t>
-  </si>
-  <si>
-    <t>Sentiment/Volatility</t>
-  </si>
-  <si>
-    <t>https://fred.stlouisfed.org/series/CHNB6FATT01CXCUQ</t>
-  </si>
-  <si>
-    <t>https://fred.stlouisfed.org/series/CHNB6FARA01CXCUQ</t>
-  </si>
-  <si>
-    <t>https://fred.stlouisfed.org/series/CHNB6CATT00CXCUQ</t>
-  </si>
-  <si>
-    <t>https://fred.stlouisfed.org/series/FEDFUNDS</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>US 10Y Treasury yield</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>Nominal Risk-free rate =</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>US Fed Fund Rate</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>US BBB Bond index yield</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>CN 10Y Government Bond Yield</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/china/interest-rate</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>CN Loan Prime Rate</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://fred.stlouisfed.org/series/BAMLC0A2CAAEY</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>US AA Bond index yield</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.spglobal.com/spdji/en/indices/fixed-income/sp-china-corporate-bond-index/#overview</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>CN AA Bond index yield</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/commodity/coal</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>Coal</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Natural </t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/commodity/natural-gas</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>Stock Indices</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>S&amp;P 500</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>3. Canada</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>DJI</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://finance.yahoo.com/quote/%5EDJI/</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://finance.yahoo.com/quote/%5EGSPC/</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>Nikkei 225</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>4. Japan</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/canada/stock-market</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>TSX</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.etnet.com.hk/www/tc/stocks/indexes_chart_interactive.php?subtype=HIS</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.sgx.com/indices/products/sti</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>STI</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>5. Singapore</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/japan/stock-market</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/stocks</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/china/stock-market</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>6. Australia</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/australia/stock-market</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>ASX</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>7. India</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/india/stock-market</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sensex</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/united-kingdom/stock-market</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>8. Britain</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>FTSE 100</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>Shanghai Composite Index</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>Hang Seng Index</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/united-states/stock-market</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
@@ -718,7 +726,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="&quot;for &quot;0&quot; Yrs&quot;"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -850,8 +858,16 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="0"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -884,30 +900,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.249977111117893"/>
-        <bgColor rgb="FFFFE599"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
+        <fgColor rgb="FF0047AB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -989,49 +993,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1045,7 +1012,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1057,49 +1023,27 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="10" fontId="2" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="10" fontId="13" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="10" fontId="15" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="15" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1164,12 +1108,19 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="10" fontId="18" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="18" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="176" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1451,276 +1402,302 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A061C73F-1F33-4614-90A5-D5D9D7C58056}">
-  <dimension ref="A2:F33"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="2.46484375" style="8" customWidth="1"/>
-    <col min="2" max="2" width="47.796875" style="8" customWidth="1"/>
-    <col min="3" max="6" width="20.796875" style="8" customWidth="1"/>
-    <col min="7" max="16384" width="8.796875" style="8"/>
+    <col min="1" max="1" width="2.46484375" style="7" customWidth="1"/>
+    <col min="2" max="2" width="47.796875" style="7" customWidth="1"/>
+    <col min="3" max="7" width="15.59765625" style="7" customWidth="1"/>
+    <col min="8" max="16384" width="8.796875" style="7"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" ht="15">
-      <c r="A2" s="3"/>
-      <c r="B2" s="2" t="s">
+    <row r="1" spans="1:7">
+      <c r="C1" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="D1" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="E1" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="F1" s="15" t="s">
+        <v>188</v>
+      </c>
+      <c r="G1" s="15" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="51"/>
+      <c r="B2" s="52" t="s">
+        <v>192</v>
+      </c>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="51"/>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="51"/>
+      <c r="B4" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="E2" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="F2" s="23" t="s">
+      <c r="C4" s="47">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="D4" s="47">
+        <v>5.2299999999999999E-2</v>
+      </c>
+      <c r="E4" s="48">
+        <f>D4-C4</f>
+        <v>1.0299999999999997E-2</v>
+      </c>
+      <c r="F4" s="48">
+        <f>G4-C4</f>
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="G4" s="48">
+        <f>MAX(C4+E4,8%)</f>
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="51"/>
+      <c r="B5" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5" s="47">
+        <v>1.8100000000000002E-2</v>
+      </c>
+      <c r="D5" s="47">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="E5" s="48">
+        <f>D5-C5</f>
+        <v>4.6899999999999997E-2</v>
+      </c>
+      <c r="F5" s="48">
+        <f>G5-C5</f>
+        <v>8.1900000000000001E-2</v>
+      </c>
+      <c r="G5" s="48">
+        <f>MAX(C5+E5,10%)</f>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="53"/>
+      <c r="B7" s="52" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="52"/>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="52"/>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="C8" s="49">
+        <v>0.15</v>
+      </c>
+      <c r="D8" s="50">
+        <v>4</v>
+      </c>
+      <c r="E8" s="50"/>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="F10" s="17"/>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="F11" s="17"/>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="B12" s="52" t="s">
+        <v>193</v>
+      </c>
+      <c r="C12" s="52"/>
+      <c r="D12" s="52"/>
+      <c r="E12" s="52"/>
+      <c r="F12" s="52"/>
+      <c r="G12" s="52"/>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="B13" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="F13" s="17"/>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="B14" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="F14" s="17"/>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="B15" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="B16" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="B17" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="C18" s="45"/>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="B19" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="B20" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="C20" s="16" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
-      <c r="B3" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="C3" s="13">
-        <v>4.2000000000000003E-2</v>
-      </c>
-      <c r="D3" s="14">
-        <v>1.8100000000000002E-2</v>
-      </c>
-      <c r="E3" s="13">
-        <v>2.7650000000000001E-2</v>
-      </c>
-      <c r="F3" s="14"/>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="B4" s="8" t="s">
+    <row r="21" spans="1:7">
+      <c r="B21" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="B22" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="13">
-        <v>5.2299999999999999E-2</v>
-      </c>
-      <c r="D4" s="14">
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="E4" s="19"/>
-      <c r="F4" s="14"/>
-    </row>
-    <row r="5" spans="1:6" ht="14.25" thickBot="1">
-      <c r="B5" s="24" t="s">
+    </row>
+    <row r="23" spans="1:7">
+      <c r="B23" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18">
-        <v>0.16</v>
-      </c>
-      <c r="E5" s="20"/>
-      <c r="F5" s="18"/>
-    </row>
-    <row r="6" spans="1:6" ht="14.25" thickTop="1">
-      <c r="B6" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="C6" s="56">
-        <f>MAX(7%,C3,C4)</f>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="D6" s="56">
-        <f>MAX(D4,C6+2%/2)</f>
-        <v>0.08</v>
-      </c>
-      <c r="E6" s="56">
-        <f>(C6+D6)/2</f>
-        <v>7.5000000000000011E-2</v>
-      </c>
-      <c r="F6" s="56"/>
-    </row>
-    <row r="8" spans="1:6" ht="15">
-      <c r="A8" s="3"/>
-      <c r="B8" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C8" s="56">
-        <v>0.15</v>
-      </c>
-      <c r="D8" s="57">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="B10" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="C10" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="E10" s="26"/>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="E11" s="26"/>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="B12" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="C12" s="25" t="s">
-        <v>149</v>
-      </c>
-      <c r="E12" s="26"/>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="B13" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="C13" s="25" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="B14" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="C14" s="25" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="B15" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="C15" s="25" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="C16" s="54"/>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="B17" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="C17" s="25" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="B18" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="C18" s="25" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="B19" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="C19" s="25" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="B20" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C20" s="25" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="B21" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C21" s="25" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="15">
-      <c r="A23" s="3"/>
-      <c r="B23" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22"/>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="B24" s="6" t="s">
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="53"/>
+      <c r="B25" s="52" t="s">
+        <v>194</v>
+      </c>
+      <c r="C25" s="52"/>
+      <c r="D25" s="52"/>
+      <c r="E25" s="52"/>
+      <c r="F25" s="52"/>
+      <c r="G25" s="52"/>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="B26" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="B28" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="C24" s="25" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="B26" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="C26" s="25" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="B27" s="6" t="s">
+      <c r="C28" s="16" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="B29" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C29" s="16" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="B30" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="B32" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="C27" s="25" t="s">
+      <c r="C32" s="16" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3">
+      <c r="B33" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C33" s="16" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
-      <c r="B28" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="C28" s="25" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="B30" s="8" t="s">
+    <row r="35" spans="2:3">
+      <c r="B35" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="C30" s="25" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="B31" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="C31" s="25" t="s">
+      <c r="C35" s="16" t="s">
         <v>100</v>
-      </c>
-    </row>
-    <row r="33" spans="2:3">
-      <c r="B33" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="C33" s="25" t="s">
-        <v>103</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="11" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="C21" r:id="rId1" xr:uid="{DB671679-E839-B64A-AD4E-6D8A323DAFC3}"/>
-    <hyperlink ref="C20" r:id="rId2" xr:uid="{9CB8AD70-9E02-9A41-8E3A-990A0C1E81AE}"/>
-    <hyperlink ref="C18" r:id="rId3" xr:uid="{45D5643F-FA1A-3C48-B2D9-4B6082295A37}"/>
-    <hyperlink ref="C13" r:id="rId4" xr:uid="{8FF27AF7-25A6-F443-A0E6-DAC1AFC8FB4A}"/>
-    <hyperlink ref="C24" r:id="rId5" xr:uid="{16104B09-A651-7A41-A777-F49F69D02554}"/>
-    <hyperlink ref="C26" r:id="rId6" xr:uid="{BFEB5D28-D16E-9545-989F-F86E412707A9}"/>
-    <hyperlink ref="C10" r:id="rId7" xr:uid="{E414D4D1-755D-2A43-AB81-B4A0517E9107}"/>
-    <hyperlink ref="C28" r:id="rId8" xr:uid="{645528C6-7225-564E-908E-A85650E1CCD6}"/>
-    <hyperlink ref="C27" r:id="rId9" xr:uid="{0B036CAC-824D-E543-8C48-9EDDC7350EA2}"/>
-    <hyperlink ref="C30" r:id="rId10" xr:uid="{EF5F9EA6-9DD5-1C42-A0E5-61DBB0A5A02F}"/>
-    <hyperlink ref="C31" r:id="rId11" xr:uid="{1DE792CC-A9C9-BB47-A69A-D22E477A4A3B}"/>
-    <hyperlink ref="C33" r:id="rId12" xr:uid="{E7131674-9823-C34D-8EBB-49D25F896885}"/>
-    <hyperlink ref="C12" r:id="rId13" xr:uid="{BD25C893-4B01-48BE-AB6E-FA9F70DB6325}"/>
-    <hyperlink ref="C17" r:id="rId14" xr:uid="{01B23463-056A-45A3-AFE5-8FCBFF68216B}"/>
-    <hyperlink ref="C15" r:id="rId15" display="https://fred.stlouisfed.org/series/BAMLC0A4CBBBEY" xr:uid="{35ACA25B-AF93-B04F-A9DD-9D3D634DC7A6}"/>
-    <hyperlink ref="C14" r:id="rId16" xr:uid="{410CC38F-2D01-4044-AE85-C4E978B37B55}"/>
-    <hyperlink ref="C19" r:id="rId17" location="overview" xr:uid="{85EC9358-C071-4DB7-96C6-D513DABB95B7}"/>
+    <hyperlink ref="C23" r:id="rId1" xr:uid="{DB671679-E839-B64A-AD4E-6D8A323DAFC3}"/>
+    <hyperlink ref="C22" r:id="rId2" xr:uid="{9CB8AD70-9E02-9A41-8E3A-990A0C1E81AE}"/>
+    <hyperlink ref="C20" r:id="rId3" xr:uid="{45D5643F-FA1A-3C48-B2D9-4B6082295A37}"/>
+    <hyperlink ref="C15" r:id="rId4" xr:uid="{8FF27AF7-25A6-F443-A0E6-DAC1AFC8FB4A}"/>
+    <hyperlink ref="C26" r:id="rId5" xr:uid="{16104B09-A651-7A41-A777-F49F69D02554}"/>
+    <hyperlink ref="C28" r:id="rId6" xr:uid="{BFEB5D28-D16E-9545-989F-F86E412707A9}"/>
+    <hyperlink ref="C13" r:id="rId7" xr:uid="{E414D4D1-755D-2A43-AB81-B4A0517E9107}"/>
+    <hyperlink ref="C30" r:id="rId8" xr:uid="{645528C6-7225-564E-908E-A85650E1CCD6}"/>
+    <hyperlink ref="C29" r:id="rId9" xr:uid="{0B036CAC-824D-E543-8C48-9EDDC7350EA2}"/>
+    <hyperlink ref="C32" r:id="rId10" xr:uid="{EF5F9EA6-9DD5-1C42-A0E5-61DBB0A5A02F}"/>
+    <hyperlink ref="C33" r:id="rId11" xr:uid="{1DE792CC-A9C9-BB47-A69A-D22E477A4A3B}"/>
+    <hyperlink ref="C35" r:id="rId12" xr:uid="{E7131674-9823-C34D-8EBB-49D25F896885}"/>
+    <hyperlink ref="C14" r:id="rId13" xr:uid="{BD25C893-4B01-48BE-AB6E-FA9F70DB6325}"/>
+    <hyperlink ref="C19" r:id="rId14" xr:uid="{01B23463-056A-45A3-AFE5-8FCBFF68216B}"/>
+    <hyperlink ref="C17" r:id="rId15" display="https://fred.stlouisfed.org/series/BAMLC0A4CBBBEY" xr:uid="{35ACA25B-AF93-B04F-A9DD-9D3D634DC7A6}"/>
+    <hyperlink ref="C16" r:id="rId16" xr:uid="{410CC38F-2D01-4044-AE85-C4E978B37B55}"/>
+    <hyperlink ref="C21" r:id="rId17" location="overview" xr:uid="{85EC9358-C071-4DB7-96C6-D513DABB95B7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" verticalDpi="0" r:id="rId18"/>
@@ -1740,245 +1717,245 @@
     <row r="2" spans="1:6" ht="15">
       <c r="A2" s="3"/>
       <c r="B2" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="B3" s="43" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="B3" s="52" t="s">
-        <v>119</v>
-      </c>
-      <c r="C3" s="16" t="s">
-        <v>139</v>
+      <c r="C3" s="13" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="B4" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>140</v>
+        <v>113</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="B5" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>141</v>
+        <v>112</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="B7" s="52" t="s">
-        <v>116</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>115</v>
+      <c r="B7" s="43" t="s">
+        <v>111</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="B8" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>133</v>
+        <v>113</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="B9" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="C9" s="16" t="s">
-        <v>135</v>
+        <v>129</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15">
       <c r="A11" s="3"/>
       <c r="B11" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="53"/>
+        <v>115</v>
+      </c>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="44"/>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="8"/>
+      <c r="A12" s="7"/>
       <c r="B12" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="7"/>
+      <c r="B14" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="C12" s="25" t="s">
-        <v>91</v>
-      </c>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="8"/>
-      <c r="B14" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="C14" s="25" t="s">
-        <v>92</v>
-      </c>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
+      <c r="C14" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="8"/>
+      <c r="A15" s="7"/>
       <c r="B15" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C15" s="27" t="s">
+      <c r="C15" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="8"/>
+      <c r="A16" s="7"/>
       <c r="B16" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C16" s="28" t="s">
+      <c r="C16" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
     </row>
     <row r="17" spans="1:3">
       <c r="B17" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="C17" s="28" t="s">
+      <c r="C17" s="19" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="15">
       <c r="A19" s="3"/>
       <c r="B19" s="2" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="20" spans="1:3">
-      <c r="B20" s="52" t="s">
-        <v>119</v>
+      <c r="B20" s="43" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="B21" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="B22" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="B23" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="B24" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
     </row>
     <row r="26" spans="1:3">
-      <c r="B26" s="52" t="s">
-        <v>122</v>
-      </c>
-      <c r="C26" s="16" t="s">
-        <v>123</v>
+      <c r="B26" s="43" t="s">
+        <v>117</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="B27" t="s">
-        <v>125</v>
-      </c>
-      <c r="C27" s="16" t="s">
-        <v>124</v>
+        <v>120</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="B28" t="s">
-        <v>126</v>
-      </c>
-      <c r="C28" s="16" t="s">
-        <v>148</v>
+        <v>121</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="B29" t="s">
-        <v>127</v>
-      </c>
-      <c r="C29" s="16" t="s">
-        <v>146</v>
+        <v>122</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="B30" t="s">
-        <v>128</v>
-      </c>
-      <c r="C30" s="16" t="s">
-        <v>147</v>
+        <v>123</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="15">
       <c r="A32" s="3"/>
       <c r="B32" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="33" spans="1:6">
-      <c r="B33" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="C33" s="16" t="s">
-        <v>130</v>
+      <c r="B33" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="B34" s="6"/>
     </row>
     <row r="35" spans="1:6">
-      <c r="B35" s="52" t="s">
+      <c r="B35" s="43" t="s">
+        <v>127</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="B36" s="43" t="s">
+        <v>131</v>
+      </c>
+      <c r="C36" s="13" t="s">
         <v>132</v>
-      </c>
-      <c r="C35" s="16" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="B36" s="52" t="s">
-        <v>136</v>
-      </c>
-      <c r="C36" s="16" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="15">
       <c r="A38" s="3"/>
       <c r="B38" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C38" s="16" t="s">
-        <v>144</v>
+        <v>140</v>
+      </c>
+      <c r="C38" s="13" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="15">
       <c r="A40" s="3"/>
-      <c r="B40" s="12" t="s">
+      <c r="B40" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="C40" s="11" t="s">
-        <v>71</v>
+      <c r="C40" s="10" t="s">
+        <v>68</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>1</v>
@@ -1986,588 +1963,588 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="4"/>
-      <c r="B41" s="45" t="s">
+      <c r="B41" s="36" t="s">
         <v>53</v>
       </c>
-      <c r="C41" s="10"/>
-      <c r="D41" s="9"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="8"/>
       <c r="E41" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="4"/>
-      <c r="B42" s="46" t="s">
+      <c r="B42" s="37" t="s">
         <v>52</v>
       </c>
-      <c r="C42" s="34" t="s">
+      <c r="C42" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="D42" s="34" t="s">
+      <c r="D42" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="E42" s="29">
+      <c r="E42" s="20">
         <f t="shared" ref="E42:F45" si="0">IF(LEFT(C42,1)="H",1,IF(LEFT(C42,1)="C",-1,0))</f>
         <v>-1</v>
       </c>
-      <c r="F42" s="29">
+      <c r="F42" s="20">
         <f t="shared" si="0"/>
         <v>-1</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="4"/>
-      <c r="B43" s="46" t="s">
+      <c r="B43" s="37" t="s">
         <v>50</v>
       </c>
-      <c r="C43" s="35" t="s">
+      <c r="C43" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="D43" s="35" t="s">
+      <c r="D43" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="E43" s="29">
+      <c r="E43" s="20">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F43" s="29">
+      <c r="F43" s="20">
         <f t="shared" si="0"/>
         <v>-1</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="4"/>
-      <c r="B44" s="46" t="s">
+      <c r="B44" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="C44" s="36" t="s">
+      <c r="C44" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="D44" s="36" t="s">
+      <c r="D44" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="E44" s="29">
+      <c r="E44" s="20">
         <f t="shared" si="0"/>
         <v>-1</v>
       </c>
-      <c r="F44" s="29">
+      <c r="F44" s="20">
         <f t="shared" si="0"/>
         <v>-1</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="4"/>
-      <c r="B45" s="47" t="s">
+      <c r="B45" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="C45" s="37" t="s">
+      <c r="C45" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="D45" s="37" t="s">
+      <c r="D45" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="E45" s="29">
+      <c r="E45" s="20">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F45" s="29">
+      <c r="F45" s="20">
         <f t="shared" si="0"/>
         <v>-1</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="4"/>
-      <c r="B46" s="48" t="s">
+      <c r="B46" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="C46" s="38" t="str">
+      <c r="C46" s="29" t="str">
         <f>IF(SUM(E42:E45)&gt;=3, "Hot", IF(SUM(E42:E45)&lt;=-3,"Cold", "Mixed"))</f>
         <v>Mixed</v>
       </c>
-      <c r="D46" s="38" t="str">
+      <c r="D46" s="29" t="str">
         <f>IF(SUM(F42:F45)&gt;=3, "Hot", IF(SUM(F42:F45)&lt;=-3,"Cold", "Mixed"))</f>
         <v>Cold</v>
       </c>
-      <c r="E46" s="29">
+      <c r="E46" s="20">
         <f>IF(LEFT(C46,1)="H",2,IF(LEFT(C46,1)="C",-1,0))</f>
         <v>0</v>
       </c>
-      <c r="F46" s="29">
+      <c r="F46" s="20">
         <f>IF(LEFT(D46,1)="H",2,IF(LEFT(D46,1)="C",-1,0))</f>
         <v>-1</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="4"/>
-      <c r="B47" s="46" t="s">
+      <c r="B47" s="37" t="s">
         <v>42</v>
       </c>
-      <c r="C47" s="34" t="s">
+      <c r="C47" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="D47" s="34" t="s">
+      <c r="D47" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="E47" s="29">
+      <c r="E47" s="20">
         <f t="shared" ref="E47:F50" si="1">IF(LEFT(C47,1)="H",1,IF(LEFT(C47,1)="C",-1,0))</f>
         <v>-1</v>
       </c>
-      <c r="F47" s="29">
+      <c r="F47" s="20">
         <f t="shared" si="1"/>
         <v>-1</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="4"/>
-      <c r="B48" s="46" t="s">
+      <c r="B48" s="37" t="s">
         <v>40</v>
       </c>
-      <c r="C48" s="34" t="s">
+      <c r="C48" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="D48" s="34" t="s">
+      <c r="D48" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="E48" s="29">
+      <c r="E48" s="20">
         <f t="shared" si="1"/>
         <v>-1</v>
       </c>
-      <c r="F48" s="29">
+      <c r="F48" s="20">
         <f t="shared" si="1"/>
         <v>-1</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="4"/>
-      <c r="B49" s="46" t="s">
+      <c r="B49" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="C49" s="37" t="s">
+      <c r="C49" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="D49" s="37" t="s">
+      <c r="D49" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="E49" s="29">
+      <c r="E49" s="20">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F49" s="29">
+      <c r="F49" s="20">
         <f t="shared" si="1"/>
         <v>-1</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="4"/>
-      <c r="B50" s="46" t="s">
+      <c r="B50" s="37" t="s">
         <v>36</v>
       </c>
-      <c r="C50" s="37" t="s">
+      <c r="C50" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="D50" s="37" t="s">
+      <c r="D50" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="E50" s="29">
+      <c r="E50" s="20">
         <f t="shared" si="1"/>
         <v>-1</v>
       </c>
-      <c r="F50" s="29">
+      <c r="F50" s="20">
         <f t="shared" si="1"/>
         <v>-1</v>
       </c>
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="4"/>
-      <c r="B51" s="48" t="s">
+      <c r="B51" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="C51" s="39" t="str">
+      <c r="C51" s="30" t="str">
         <f>IF(SUM(E47:E50)&gt;=3, "Hot", IF(SUM(E47:E50)&lt;=-3,"Cold", "Mixed"))</f>
         <v>Cold</v>
       </c>
-      <c r="D51" s="39" t="str">
+      <c r="D51" s="30" t="str">
         <f>IF(SUM(F47:F50)&gt;=3, "Hot", IF(SUM(F47:F50)&lt;=-3,"Cold", "Mixed"))</f>
         <v>Cold</v>
       </c>
-      <c r="E51" s="29">
+      <c r="E51" s="20">
         <f>IF(LEFT(C51,1)="H",2,IF(LEFT(C51,1)="C",-1,0))</f>
         <v>-1</v>
       </c>
-      <c r="F51" s="29">
+      <c r="F51" s="20">
         <f>IF(LEFT(D51,1)="H",2,IF(LEFT(D51,1)="C",-1,0))</f>
         <v>-1</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="27.75">
       <c r="A52" s="4"/>
-      <c r="B52" s="46" t="s">
+      <c r="B52" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="C52" s="34" t="s">
+      <c r="C52" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="D52" s="34" t="s">
+      <c r="D52" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="E52" s="29">
+      <c r="E52" s="20">
         <f t="shared" ref="E52:F55" si="2">IF(LEFT(C52,1)="H",1,IF(LEFT(C52,1)="C",-1,0))</f>
         <v>1</v>
       </c>
-      <c r="F52" s="29">
+      <c r="F52" s="20">
         <f t="shared" si="2"/>
         <v>-1</v>
       </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="4"/>
-      <c r="B53" s="46" t="s">
+      <c r="B53" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="C53" s="34" t="s">
+      <c r="C53" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="D53" s="34" t="s">
+      <c r="D53" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="E53" s="29">
+      <c r="E53" s="20">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F53" s="29">
+      <c r="F53" s="20">
         <f t="shared" si="2"/>
         <v>-1</v>
       </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="4"/>
-      <c r="B54" s="46" t="s">
+      <c r="B54" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="C54" s="34" t="s">
+      <c r="C54" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="D54" s="34" t="s">
+      <c r="D54" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="E54" s="29">
+      <c r="E54" s="20">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F54" s="29">
+      <c r="F54" s="20">
         <f t="shared" si="2"/>
         <v>-1</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="4"/>
-      <c r="B55" s="46" t="s">
+      <c r="B55" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="C55" s="34" t="s">
+      <c r="C55" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="D55" s="34" t="s">
+      <c r="D55" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="E55" s="29">
+      <c r="E55" s="20">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F55" s="29">
+      <c r="F55" s="20">
         <f t="shared" si="2"/>
         <v>-1</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="4"/>
-      <c r="B56" s="48" t="s">
+      <c r="B56" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="C56" s="39" t="str">
+      <c r="C56" s="30" t="str">
         <f>IF(SUM(E52:E55)&gt;=3, "Hot", IF(SUM(E52:E55)&lt;=-3,"Cold", "Mixed"))</f>
         <v>Mixed</v>
       </c>
-      <c r="D56" s="39" t="str">
+      <c r="D56" s="30" t="str">
         <f>IF(SUM(F52:F55)&gt;=3, "Hot", IF(SUM(F52:F55)&lt;=-3,"Cold", "Mixed"))</f>
         <v>Cold</v>
       </c>
-      <c r="E56" s="29">
+      <c r="E56" s="20">
         <f>IF(LEFT(C56,1)="H",2,IF(LEFT(C56,1)="C",-1,0))</f>
         <v>0</v>
       </c>
-      <c r="F56" s="29">
+      <c r="F56" s="20">
         <f>IF(LEFT(D56,1)="H",2,IF(LEFT(D56,1)="C",-1,0))</f>
         <v>-1</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="27.75">
       <c r="A57" s="4"/>
-      <c r="B57" s="46" t="s">
+      <c r="B57" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="C57" s="34" t="s">
+      <c r="C57" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="D57" s="34" t="s">
+      <c r="D57" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="E57" s="29">
+      <c r="E57" s="20">
         <f t="shared" ref="E57:F60" si="3">IF(LEFT(C57,1)="H",1,IF(LEFT(C57,1)="C",-1,0))</f>
         <v>0</v>
       </c>
-      <c r="F57" s="29">
+      <c r="F57" s="20">
         <f t="shared" si="3"/>
         <v>-1</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="27.75">
       <c r="A58" s="4"/>
-      <c r="B58" s="46" t="s">
+      <c r="B58" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="C58" s="34" t="s">
+      <c r="C58" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="D58" s="34" t="s">
+      <c r="D58" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="E58" s="29">
+      <c r="E58" s="20">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F58" s="29">
+      <c r="F58" s="20">
         <f t="shared" si="3"/>
         <v>-1</v>
       </c>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="4"/>
-      <c r="B59" s="46" t="s">
+      <c r="B59" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="C59" s="34" t="s">
+      <c r="C59" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="D59" s="34" t="s">
+      <c r="D59" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="E59" s="29">
+      <c r="E59" s="20">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="F59" s="29">
+      <c r="F59" s="20">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="27.75">
       <c r="A60" s="4"/>
-      <c r="B60" s="46" t="s">
+      <c r="B60" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="C60" s="34" t="s">
+      <c r="C60" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="D60" s="34" t="s">
+      <c r="D60" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="E60" s="29">
+      <c r="E60" s="20">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F60" s="29">
+      <c r="F60" s="20">
         <f t="shared" si="3"/>
         <v>-1</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="4"/>
-      <c r="B61" s="48" t="s">
+      <c r="B61" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="C61" s="39" t="str">
+      <c r="C61" s="30" t="str">
         <f>IF(SUM(E57:E60)&gt;=3, "Hot", IF(SUM(E57:E60)&lt;=-3,"Cold", "Mixed"))</f>
         <v>Mixed</v>
       </c>
-      <c r="D61" s="39" t="str">
+      <c r="D61" s="30" t="str">
         <f>IF(SUM(F57:F60)&gt;=3, "Hot", IF(SUM(F57:F60)&lt;=-3,"Cold", "Mixed"))</f>
         <v>Cold</v>
       </c>
-      <c r="E61" s="29">
+      <c r="E61" s="20">
         <f>IF(LEFT(C61,1)="H",2,IF(LEFT(C61,1)="C",-1,0))</f>
         <v>0</v>
       </c>
-      <c r="F61" s="29">
+      <c r="F61" s="20">
         <f>IF(LEFT(D61,1)="H",2,IF(LEFT(D61,1)="C",-1,0))</f>
         <v>-1</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="27.75">
       <c r="A62" s="4"/>
-      <c r="B62" s="49" t="s">
+      <c r="B62" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="C62" s="40" t="str">
+      <c r="C62" s="31" t="str">
         <f>IF(OR(E62=4,E62=-4),"In extreme",IF(E62=0,"In equilibrium",IF(OR(E62&gt;0),"Relatively optimistic","Relatively pessimistic")))</f>
         <v>Relatively pessimistic</v>
       </c>
-      <c r="D62" s="40" t="str">
+      <c r="D62" s="31" t="str">
         <f>IF(OR(F62=4,F62=-4),"In extreme",IF(F62=0,"In equilibrium",IF(OR(F62&gt;0),"Relatively optimistic","Relatively pessimistic")))</f>
         <v>In extreme</v>
       </c>
-      <c r="E62" s="30">
+      <c r="E62" s="21">
         <f>SUM(E46,E51,E56,E61)</f>
         <v>-1</v>
       </c>
-      <c r="F62" s="30">
+      <c r="F62" s="21">
         <f>SUM(F46,F51,F56,F61)</f>
         <v>-4</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="4"/>
-      <c r="B63" s="41"/>
-      <c r="C63" s="41"/>
-      <c r="D63" s="41"/>
-      <c r="E63" s="31"/>
-      <c r="F63" s="31"/>
+      <c r="B63" s="32"/>
+      <c r="C63" s="32"/>
+      <c r="D63" s="32"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="4"/>
-      <c r="B64" s="50" t="s">
+      <c r="B64" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="C64" s="42" t="s">
+      <c r="C64" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="D64" s="42" t="s">
+      <c r="D64" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="E64" s="32"/>
-      <c r="F64" s="32"/>
+      <c r="E64" s="23"/>
+      <c r="F64" s="23"/>
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="4"/>
-      <c r="B65" s="47" t="s">
+      <c r="B65" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="C65" s="37" t="s">
+      <c r="C65" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="D65" s="37" t="s">
+      <c r="D65" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="E65" s="32">
+      <c r="E65" s="23">
         <f t="shared" ref="E65:F69" si="4">IF(LEFT(C65,1)="H",2,IF(LEFT(C65,1)="C",0,1))</f>
         <v>2</v>
       </c>
-      <c r="F65" s="32">
+      <c r="F65" s="23">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:6">
-      <c r="B66" s="47" t="s">
+      <c r="B66" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="C66" s="43" t="e">
+      <c r="C66" s="34" t="e">
         <f>IF(Macro!#REF!&gt;=3%, "Hot - High", IF(Macro!#REF!&lt;=1.5%, "Cold - Low", "Mixed - Dormant"))</f>
         <v>#REF!</v>
       </c>
-      <c r="D66" s="43" t="e">
+      <c r="D66" s="34" t="e">
         <f>IF(Macro!#REF!&gt;=3%, "Hot - High", IF(Macro!#REF!&lt;=1.5%, "Cold - Low", "Mixed - Dormant"))</f>
         <v>#REF!</v>
       </c>
-      <c r="E66" s="32" t="e">
+      <c r="E66" s="23" t="e">
         <f t="shared" si="4"/>
         <v>#REF!</v>
       </c>
-      <c r="F66" s="32" t="e">
+      <c r="F66" s="23" t="e">
         <f t="shared" si="4"/>
         <v>#REF!</v>
       </c>
     </row>
     <row r="67" spans="1:6">
-      <c r="B67" s="47" t="s">
+      <c r="B67" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="C67" s="43" t="str">
+      <c r="C67" s="34" t="str">
         <f>C43</f>
         <v>Hot - Positive</v>
       </c>
-      <c r="D67" s="43" t="str">
+      <c r="D67" s="34" t="str">
         <f>D43</f>
         <v>Cold - Negative</v>
       </c>
-      <c r="E67" s="32">
+      <c r="E67" s="23">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="F67" s="32">
+      <c r="F67" s="23">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:6">
-      <c r="B68" s="47" t="s">
+      <c r="B68" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="C68" s="43" t="str">
+      <c r="C68" s="34" t="str">
         <f>C49</f>
         <v>Mixed</v>
       </c>
-      <c r="D68" s="43" t="str">
+      <c r="D68" s="34" t="str">
         <f>D49</f>
         <v>Cold - High</v>
       </c>
-      <c r="E68" s="32">
+      <c r="E68" s="23">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="F68" s="32">
+      <c r="F68" s="23">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="47" t="s">
+      <c r="B69" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="C69" s="43" t="str">
+      <c r="C69" s="34" t="str">
         <f>C50</f>
         <v>Cold - Wide</v>
       </c>
-      <c r="D69" s="43" t="str">
+      <c r="D69" s="34" t="str">
         <f>D50</f>
         <v>Cold - Wide</v>
       </c>
-      <c r="E69" s="32">
+      <c r="E69" s="23">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F69" s="32">
+      <c r="F69" s="23">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:6">
-      <c r="B70" s="51" t="s">
+      <c r="B70" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="C70" s="44" t="e">
+      <c r="C70" s="35" t="e">
         <f>Macro!#REF!*(1+E70)</f>
         <v>#REF!</v>
       </c>
-      <c r="D70" s="44" t="e">
+      <c r="D70" s="35" t="e">
         <f>Macro!#REF!*(1+F70)</f>
         <v>#REF!</v>
       </c>
-      <c r="E70" s="33" t="e">
+      <c r="E70" s="24" t="e">
         <f>SUM(E65:E69)/10</f>
         <v>#REF!</v>
       </c>
-      <c r="F70" s="33" t="e">
+      <c r="F70" s="24" t="e">
         <f>SUM(F65:F69)/10</f>
         <v>#REF!</v>
       </c>
@@ -2667,74 +2644,74 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3">
-      <c r="B2" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="C2" s="16" t="s">
-        <v>142</v>
+      <c r="B2" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="2:3">
-      <c r="B4" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>80</v>
+      <c r="B4" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="2:3">
-      <c r="B6" s="15" t="s">
-        <v>75</v>
+      <c r="B6" s="12" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="2:3">
       <c r="B7" t="s">
-        <v>73</v>
-      </c>
-      <c r="C7" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3">
+      <c r="B8" s="46" t="s">
+        <v>157</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3">
+      <c r="B9" s="46" t="s">
+        <v>156</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3">
+      <c r="B11" s="14" t="s">
         <v>74</v>
-      </c>
-    </row>
-    <row r="8" spans="2:3">
-      <c r="B8" s="55" t="s">
-        <v>163</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="9" spans="2:3">
-      <c r="B9" s="55" t="s">
-        <v>162</v>
-      </c>
-      <c r="C9" s="16" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="11" spans="2:3">
-      <c r="B11" s="21" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="12" spans="2:3">
       <c r="B12" t="s">
-        <v>76</v>
-      </c>
-      <c r="C12" s="16" t="s">
-        <v>78</v>
+        <v>73</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="14" spans="2:3">
-      <c r="B14" s="15" t="s">
-        <v>83</v>
+      <c r="B14" s="12" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="15" spans="2:3">
       <c r="B15" t="s">
-        <v>82</v>
-      </c>
-      <c r="C15" s="16" t="s">
-        <v>81</v>
+        <v>79</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -2764,18 +2741,18 @@
   <sheetData>
     <row r="2" spans="2:4">
       <c r="C2" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="2:4">
       <c r="B3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="16" t="s">
-        <v>104</v>
+      <c r="C3" s="13" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="2:4">
@@ -2785,22 +2762,22 @@
     </row>
     <row r="7" spans="2:4">
       <c r="B7" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="2:4">
       <c r="B9" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11" spans="2:4">
       <c r="B11" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13" spans="2:4">
       <c r="B13" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -2817,143 +2794,143 @@
   <dimension ref="A2:C27"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="2.46484375" style="8" customWidth="1"/>
-    <col min="2" max="2" width="41.796875" style="8" customWidth="1"/>
-    <col min="3" max="6" width="20.796875" style="8" customWidth="1"/>
-    <col min="7" max="16384" width="8.796875" style="8"/>
+    <col min="1" max="1" width="2.46484375" style="7" customWidth="1"/>
+    <col min="2" max="2" width="41.796875" style="7" customWidth="1"/>
+    <col min="3" max="6" width="20.796875" style="7" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="7"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:3" ht="15">
       <c r="A2" s="3"/>
       <c r="B2" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="C2" s="25" t="s">
-        <v>180</v>
+        <v>159</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="B3" s="52" t="s">
-        <v>119</v>
-      </c>
-      <c r="C3" s="25" t="s">
-        <v>193</v>
+      <c r="B3" s="43" t="s">
+        <v>114</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="B4" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="C4" s="25" t="s">
-        <v>170</v>
+        <v>160</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="B5" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="C5" s="25" t="s">
-        <v>169</v>
+        <v>162</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="B7" s="52" t="s">
-        <v>116</v>
-      </c>
-      <c r="C7" s="25"/>
+      <c r="B7" s="43" t="s">
+        <v>111</v>
+      </c>
+      <c r="C7" s="16"/>
     </row>
     <row r="8" spans="1:3">
       <c r="B8" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="C8" s="25" t="s">
-        <v>181</v>
+        <v>185</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="B9" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="C9" s="25" t="s">
-        <v>175</v>
+        <v>186</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="B11" s="52" t="s">
+      <c r="B11" s="43" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="B12" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="C12" s="16" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
-      <c r="B12" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="C12" s="25" t="s">
+    <row r="14" spans="1:3">
+      <c r="B14" s="43" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="B15" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="C15" s="16" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
-      <c r="B14" s="52" t="s">
+    <row r="17" spans="2:3">
+      <c r="B17" s="43" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
-      <c r="B15" s="8" t="s">
+    <row r="18" spans="2:3">
+      <c r="B18" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="C15" s="25" t="s">
+      <c r="C18" s="16" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3">
+      <c r="B20" s="43" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3">
+      <c r="B21" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3">
+      <c r="B23" s="43" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="17" spans="2:3">
-      <c r="B17" s="52" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3">
-      <c r="B18" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="C18" s="25" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="20" spans="2:3">
-      <c r="B20" s="52" t="s">
+    <row r="24" spans="2:3">
+      <c r="B24" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3">
+      <c r="B26" s="43" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3">
+      <c r="B27" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="C27" s="16" t="s">
         <v>182</v>
-      </c>
-    </row>
-    <row r="21" spans="2:3">
-      <c r="B21" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="C21" s="25" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="23" spans="2:3">
-      <c r="B23" s="52" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="24" spans="2:3">
-      <c r="B24" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="C24" s="25" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="26" spans="2:3">
-      <c r="B26" s="52" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="27" spans="2:3">
-      <c r="B27" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="C27" s="25" t="s">
-        <v>188</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/Macro_Monitor.xlsx
+++ b/financial_models/Macro_Monitor.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32A207E0-0677-468C-B427-147244F02532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4B82A0B-EDC0-427F-AC2A-3CC082478A84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Macro" sheetId="2" r:id="rId1"/>
-    <sheet name="Economics" sheetId="4" r:id="rId2"/>
-    <sheet name="Commodities" sheetId="5" r:id="rId3"/>
-    <sheet name="RE" sheetId="6" r:id="rId4"/>
-    <sheet name="Equity" sheetId="8" r:id="rId5"/>
+    <sheet name="Market_Yield" sheetId="2" r:id="rId1"/>
+    <sheet name="Forex" sheetId="9" r:id="rId2"/>
+    <sheet name="Equity_Indices" sheetId="8" r:id="rId3"/>
+    <sheet name="Economies" sheetId="4" r:id="rId4"/>
+    <sheet name="Commodities" sheetId="5" r:id="rId5"/>
+    <sheet name="Real_Estate" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="198">
   <si>
     <t>China</t>
   </si>
@@ -289,10 +290,6 @@
     <t>CN</t>
   </si>
   <si>
-    <t>Target Return</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
     <t>Crude oil</t>
   </si>
   <si>
@@ -497,225 +494,242 @@
     <t>https://tradingeconomics.com/commodity/crb</t>
   </si>
   <si>
+    <t>https://fred.stlouisfed.org/series/VIXCLS</t>
+  </si>
+  <si>
+    <t>Sentiment/Volatility</t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/series/CHNB6FATT01CXCUQ</t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/series/CHNB6FARA01CXCUQ</t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/series/CHNB6CATT00CXCUQ</t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/series/FEDFUNDS</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>US 10Y Treasury yield</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>US Fed Fund Rate</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>US BBB Bond index yield</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>CN 10Y Government Bond Yield</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/china/interest-rate</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>CN Loan Prime Rate</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/series/BAMLC0A2CAAEY</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>US AA Bond index yield</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.spglobal.com/spdji/en/indices/fixed-income/sp-china-corporate-bond-index/#overview</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>CN AA Bond index yield</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/commodity/coal</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Coal</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Natural </t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/commodity/natural-gas</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stock Indices</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>S&amp;P 500</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>3. Canada</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>DJI</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://finance.yahoo.com/quote/%5EDJI/</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://finance.yahoo.com/quote/%5EGSPC/</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Nikkei 225</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>4. Japan</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/canada/stock-market</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>TSX</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.etnet.com.hk/www/tc/stocks/indexes_chart_interactive.php?subtype=HIS</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.sgx.com/indices/products/sti</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>STI</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>5. Singapore</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/japan/stock-market</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/stocks</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/china/stock-market</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>6. Australia</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/australia/stock-market</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>ASX</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>7. India</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/india/stock-market</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sensex</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/united-kingdom/stock-market</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>8. Britain</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>FTSE 100</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shanghai Composite Index</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hang Seng Index</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/united-states/stock-market</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>ERP</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bond Premium</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equity Cost</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Nominal Rf rate</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Market Yields:</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Notes</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Forex</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Valuation Model Assumptions</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
     <t>CRB Commodity Index</t>
-  </si>
-  <si>
-    <t>https://fred.stlouisfed.org/series/VIXCLS</t>
-  </si>
-  <si>
-    <t>Sentiment/Volatility</t>
-  </si>
-  <si>
-    <t>https://fred.stlouisfed.org/series/CHNB6FATT01CXCUQ</t>
-  </si>
-  <si>
-    <t>https://fred.stlouisfed.org/series/CHNB6FARA01CXCUQ</t>
-  </si>
-  <si>
-    <t>https://fred.stlouisfed.org/series/CHNB6CATT00CXCUQ</t>
-  </si>
-  <si>
-    <t>https://fred.stlouisfed.org/series/FEDFUNDS</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>US 10Y Treasury yield</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>US Fed Fund Rate</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>US BBB Bond index yield</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>CN 10Y Government Bond Yield</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/china/interest-rate</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>CN Loan Prime Rate</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://fred.stlouisfed.org/series/BAMLC0A2CAAEY</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>US AA Bond index yield</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.spglobal.com/spdji/en/indices/fixed-income/sp-china-corporate-bond-index/#overview</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>CN AA Bond index yield</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/commodity/coal</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>Coal</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Natural </t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/commodity/natural-gas</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>Stock Indices</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>S&amp;P 500</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>3. Canada</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>DJI</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://finance.yahoo.com/quote/%5EDJI/</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://finance.yahoo.com/quote/%5EGSPC/</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>Nikkei 225</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>4. Japan</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/canada/stock-market</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>TSX</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.etnet.com.hk/www/tc/stocks/indexes_chart_interactive.php?subtype=HIS</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.sgx.com/indices/products/sti</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>STI</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>5. Singapore</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/japan/stock-market</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/stocks</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/china/stock-market</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>6. Australia</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/australia/stock-market</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>ASX</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>7. India</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/india/stock-market</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sensex</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/united-kingdom/stock-market</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>8. Britain</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>FTSE 100</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>Shanghai Composite Index</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>Hang Seng Index</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/united-states/stock-market</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>ERP</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bond Premium</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>Equity Cost</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>Nominal Rf rate</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>Market Yields:</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>Notes</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>Forex</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Commodities</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Real Estate</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Target Annual Return</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
@@ -726,7 +740,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="&quot;for &quot;0&quot; Yrs&quot;"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -858,16 +872,8 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color theme="0"/>
-      <name val="Microsoft YaHei"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -901,12 +907,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-9.9978637043366805E-2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF0047AB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1108,19 +1108,19 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1402,7 +1402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A061C73F-1F33-4614-90A5-D5D9D7C58056}">
-  <dimension ref="A1:G35"/>
+  <dimension ref="A2:G32"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="2.46484375" style="7" customWidth="1"/>
@@ -1411,300 +1411,536 @@
     <col min="8" max="16384" width="8.796875" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="C1" s="15" t="s">
+    <row r="2" spans="1:7" ht="15">
+      <c r="A2" s="3"/>
+      <c r="B2" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C2" s="52"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="51"/>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="4"/>
+      <c r="B3" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="C3" s="49">
+        <v>0.2</v>
+      </c>
+      <c r="D3" s="50">
+        <v>3</v>
+      </c>
+      <c r="E3" s="50"/>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="4"/>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="4"/>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="4"/>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="C10" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>187</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="G10" s="15" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15">
+      <c r="A11" s="3"/>
+      <c r="B11" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C11" s="52"/>
+      <c r="D11" s="53"/>
+      <c r="E11" s="52"/>
+      <c r="F11" s="53"/>
+      <c r="G11" s="51"/>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="B13" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="47">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="D13" s="47">
+        <v>5.2299999999999999E-2</v>
+      </c>
+      <c r="E13" s="48">
+        <f>D13-C13</f>
+        <v>1.0299999999999997E-2</v>
+      </c>
+      <c r="F13" s="48">
+        <f>G13-C13</f>
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="G13" s="48">
+        <f>MAX(C13+E13,8%)</f>
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="B14" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="C14" s="47">
+        <v>1.8100000000000002E-2</v>
+      </c>
+      <c r="D14" s="47">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="E14" s="48">
+        <f>D14-C14</f>
+        <v>4.6899999999999997E-2</v>
+      </c>
+      <c r="F14" s="48">
+        <f>G14-C14</f>
+        <v>8.1900000000000001E-2</v>
+      </c>
+      <c r="G14" s="48">
+        <f>MAX(C14+E14,10%)</f>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="F17" s="17"/>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="F18" s="17"/>
+    </row>
+    <row r="19" spans="1:7" ht="15">
+      <c r="A19" s="3"/>
+      <c r="B19" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="D1" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="E1" s="15" t="s">
-        <v>189</v>
-      </c>
-      <c r="F1" s="15" t="s">
-        <v>188</v>
-      </c>
-      <c r="G1" s="15" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="51"/>
-      <c r="B2" s="52" t="s">
-        <v>192</v>
-      </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="51"/>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="51"/>
-      <c r="B4" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="47">
-        <v>4.2000000000000003E-2</v>
-      </c>
-      <c r="D4" s="47">
-        <v>5.2299999999999999E-2</v>
-      </c>
-      <c r="E4" s="48">
-        <f>D4-C4</f>
-        <v>1.0299999999999997E-2</v>
-      </c>
-      <c r="F4" s="48">
-        <f>G4-C4</f>
-        <v>3.7999999999999999E-2</v>
-      </c>
-      <c r="G4" s="48">
-        <f>MAX(C4+E4,8%)</f>
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="51"/>
-      <c r="B5" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="C5" s="47">
-        <v>1.8100000000000002E-2</v>
-      </c>
-      <c r="D5" s="47">
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="E5" s="48">
-        <f>D5-C5</f>
-        <v>4.6899999999999997E-2</v>
-      </c>
-      <c r="F5" s="48">
-        <f>G5-C5</f>
-        <v>8.1900000000000001E-2</v>
-      </c>
-      <c r="G5" s="48">
-        <f>MAX(C5+E5,10%)</f>
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="53"/>
-      <c r="B7" s="52" t="s">
-        <v>69</v>
-      </c>
-      <c r="C7" s="52"/>
-      <c r="D7" s="52"/>
-      <c r="E7" s="52"/>
-      <c r="F7" s="52"/>
-      <c r="G7" s="52"/>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="C8" s="49">
-        <v>0.15</v>
-      </c>
-      <c r="D8" s="50">
-        <v>4</v>
-      </c>
-      <c r="E8" s="50"/>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="F10" s="17"/>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="F11" s="17"/>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="B12" s="52" t="s">
-        <v>193</v>
-      </c>
-      <c r="C12" s="52"/>
-      <c r="D12" s="52"/>
-      <c r="E12" s="52"/>
-      <c r="F12" s="52"/>
-      <c r="G12" s="52"/>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="B13" s="7" t="s">
+      <c r="C19" s="52"/>
+      <c r="D19" s="53"/>
+      <c r="E19" s="52"/>
+      <c r="F19" s="53"/>
+      <c r="G19" s="51"/>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="B20" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C20" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="C13" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="F13" s="17"/>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="B14" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="C14" s="16" t="s">
+      <c r="F20" s="17"/>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="B21" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="F14" s="17"/>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="B15" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="C15" s="16" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="B16" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C16" s="16" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="B17" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="C17" s="16" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="C18" s="45"/>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="B19" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="C19" s="16" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="B20" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="C20" s="16" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="B21" s="4" t="s">
-        <v>154</v>
-      </c>
       <c r="C21" s="16" t="s">
-        <v>153</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="F21" s="17"/>
     </row>
     <row r="22" spans="1:7">
       <c r="B22" s="4" t="s">
-        <v>65</v>
+        <v>143</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="B23" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="B24" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="C25" s="45"/>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="B26" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="B27" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="B28" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="B29" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C29" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="B30" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="C23" s="16" t="s">
+      <c r="C30" s="16" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="53"/>
-      <c r="B25" s="52" t="s">
-        <v>194</v>
-      </c>
-      <c r="C25" s="52"/>
-      <c r="D25" s="52"/>
-      <c r="E25" s="52"/>
-      <c r="F25" s="52"/>
-      <c r="G25" s="52"/>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="B26" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="C26" s="16" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="B28" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="C28" s="16" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="B29" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C29" s="16" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="B30" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="C30" s="16" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="B32" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="C32" s="16" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="33" spans="2:3">
-      <c r="B33" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="C33" s="16" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="35" spans="2:3">
-      <c r="B35" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="C35" s="16" t="s">
-        <v>100</v>
-      </c>
+    <row r="32" spans="1:7" ht="15">
+      <c r="F32" s="53"/>
+      <c r="G32" s="51"/>
     </row>
   </sheetData>
   <phoneticPr fontId="11" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="C23" r:id="rId1" xr:uid="{DB671679-E839-B64A-AD4E-6D8A323DAFC3}"/>
-    <hyperlink ref="C22" r:id="rId2" xr:uid="{9CB8AD70-9E02-9A41-8E3A-990A0C1E81AE}"/>
-    <hyperlink ref="C20" r:id="rId3" xr:uid="{45D5643F-FA1A-3C48-B2D9-4B6082295A37}"/>
-    <hyperlink ref="C15" r:id="rId4" xr:uid="{8FF27AF7-25A6-F443-A0E6-DAC1AFC8FB4A}"/>
-    <hyperlink ref="C26" r:id="rId5" xr:uid="{16104B09-A651-7A41-A777-F49F69D02554}"/>
-    <hyperlink ref="C28" r:id="rId6" xr:uid="{BFEB5D28-D16E-9545-989F-F86E412707A9}"/>
-    <hyperlink ref="C13" r:id="rId7" xr:uid="{E414D4D1-755D-2A43-AB81-B4A0517E9107}"/>
-    <hyperlink ref="C30" r:id="rId8" xr:uid="{645528C6-7225-564E-908E-A85650E1CCD6}"/>
-    <hyperlink ref="C29" r:id="rId9" xr:uid="{0B036CAC-824D-E543-8C48-9EDDC7350EA2}"/>
-    <hyperlink ref="C32" r:id="rId10" xr:uid="{EF5F9EA6-9DD5-1C42-A0E5-61DBB0A5A02F}"/>
-    <hyperlink ref="C33" r:id="rId11" xr:uid="{1DE792CC-A9C9-BB47-A69A-D22E477A4A3B}"/>
-    <hyperlink ref="C35" r:id="rId12" xr:uid="{E7131674-9823-C34D-8EBB-49D25F896885}"/>
-    <hyperlink ref="C14" r:id="rId13" xr:uid="{BD25C893-4B01-48BE-AB6E-FA9F70DB6325}"/>
-    <hyperlink ref="C19" r:id="rId14" xr:uid="{01B23463-056A-45A3-AFE5-8FCBFF68216B}"/>
-    <hyperlink ref="C17" r:id="rId15" display="https://fred.stlouisfed.org/series/BAMLC0A4CBBBEY" xr:uid="{35ACA25B-AF93-B04F-A9DD-9D3D634DC7A6}"/>
-    <hyperlink ref="C16" r:id="rId16" xr:uid="{410CC38F-2D01-4044-AE85-C4E978B37B55}"/>
-    <hyperlink ref="C21" r:id="rId17" location="overview" xr:uid="{85EC9358-C071-4DB7-96C6-D513DABB95B7}"/>
+    <hyperlink ref="C30" r:id="rId1" xr:uid="{DB671679-E839-B64A-AD4E-6D8A323DAFC3}"/>
+    <hyperlink ref="C29" r:id="rId2" xr:uid="{9CB8AD70-9E02-9A41-8E3A-990A0C1E81AE}"/>
+    <hyperlink ref="C27" r:id="rId3" xr:uid="{45D5643F-FA1A-3C48-B2D9-4B6082295A37}"/>
+    <hyperlink ref="C22" r:id="rId4" xr:uid="{8FF27AF7-25A6-F443-A0E6-DAC1AFC8FB4A}"/>
+    <hyperlink ref="C20" r:id="rId5" xr:uid="{E414D4D1-755D-2A43-AB81-B4A0517E9107}"/>
+    <hyperlink ref="C21" r:id="rId6" xr:uid="{BD25C893-4B01-48BE-AB6E-FA9F70DB6325}"/>
+    <hyperlink ref="C26" r:id="rId7" xr:uid="{01B23463-056A-45A3-AFE5-8FCBFF68216B}"/>
+    <hyperlink ref="C24" r:id="rId8" display="https://fred.stlouisfed.org/series/BAMLC0A4CBBBEY" xr:uid="{35ACA25B-AF93-B04F-A9DD-9D3D634DC7A6}"/>
+    <hyperlink ref="C23" r:id="rId9" xr:uid="{410CC38F-2D01-4044-AE85-C4E978B37B55}"/>
+    <hyperlink ref="C28" r:id="rId10" location="overview" xr:uid="{85EC9358-C071-4DB7-96C6-D513DABB95B7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId18"/>
+  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId11"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{313BBC5B-4592-4EC9-BE37-C083F15EE9CA}">
+  <dimension ref="A2:E12"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
+  <cols>
+    <col min="1" max="1" width="2.46484375" customWidth="1"/>
+    <col min="2" max="2" width="27.9296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:5" ht="15">
+      <c r="A2" s="3"/>
+      <c r="B2" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C2" s="52"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="52"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="7"/>
+      <c r="B3" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="7"/>
+      <c r="B5" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="7"/>
+      <c r="B6" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="7"/>
+      <c r="B9" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="7"/>
+      <c r="B12" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="11" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="C3" r:id="rId1" xr:uid="{16104B09-A651-7A41-A777-F49F69D02554}"/>
+    <hyperlink ref="C5" r:id="rId2" xr:uid="{BFEB5D28-D16E-9545-989F-F86E412707A9}"/>
+    <hyperlink ref="C7" r:id="rId3" xr:uid="{645528C6-7225-564E-908E-A85650E1CCD6}"/>
+    <hyperlink ref="C6" r:id="rId4" xr:uid="{0B036CAC-824D-E543-8C48-9EDDC7350EA2}"/>
+    <hyperlink ref="C9" r:id="rId5" xr:uid="{EF5F9EA6-9DD5-1C42-A0E5-61DBB0A5A02F}"/>
+    <hyperlink ref="C10" r:id="rId6" xr:uid="{1DE792CC-A9C9-BB47-A69A-D22E477A4A3B}"/>
+    <hyperlink ref="C12" r:id="rId7" xr:uid="{E7131674-9823-C34D-8EBB-49D25F896885}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B29DA212-C2AF-4D3E-9C01-BCAB145BF990}">
+  <dimension ref="A2:C27"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="13.9"/>
+  <cols>
+    <col min="1" max="1" width="2.46484375" style="7" customWidth="1"/>
+    <col min="2" max="2" width="41.796875" style="7" customWidth="1"/>
+    <col min="3" max="6" width="20.796875" style="7" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="7"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:3" ht="15">
+      <c r="A2" s="3"/>
+      <c r="B2" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="B3" s="43" t="s">
+        <v>113</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="B4" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="B5" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="B7" s="43" t="s">
+        <v>110</v>
+      </c>
+      <c r="C7" s="16"/>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="B8" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="B9" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="B11" s="43" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="B12" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="B14" s="43" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="B15" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3">
+      <c r="B17" s="43" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3">
+      <c r="B18" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3">
+      <c r="B20" s="43" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3">
+      <c r="B21" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3">
+      <c r="B23" s="43" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3">
+      <c r="B24" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3">
+      <c r="B26" s="43" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3">
+      <c r="B27" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>180</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="11" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="C5" r:id="rId1" xr:uid="{7EA46E5E-057B-48C9-8A0D-B56B623EF344}"/>
+    <hyperlink ref="C4" r:id="rId2" xr:uid="{8FF96C9D-4D1A-4741-A8FC-C93FF0BAEB17}"/>
+    <hyperlink ref="C12" r:id="rId3" xr:uid="{7720DD14-3F75-4F25-8D70-F6180ED9FB8E}"/>
+    <hyperlink ref="C9" r:id="rId4" xr:uid="{24CE27D2-F11F-4C96-99C0-31B5BD7EA483}"/>
+    <hyperlink ref="C18" r:id="rId5" xr:uid="{09648102-1869-492C-87E8-7FC427C0F56E}"/>
+    <hyperlink ref="C15" r:id="rId6" xr:uid="{2EDD765B-40DE-4D2D-9531-556EBBD3F442}"/>
+    <hyperlink ref="C2" r:id="rId7" xr:uid="{7787D8AC-7779-42B9-928B-03FC735FB8BD}"/>
+    <hyperlink ref="C8" r:id="rId8" xr:uid="{BA156D29-558F-489F-A67F-2DF63DB9298F}"/>
+    <hyperlink ref="C21" r:id="rId9" xr:uid="{7654C459-BEF7-4D12-A6F9-A473435AB19D}"/>
+    <hyperlink ref="C24" r:id="rId10" xr:uid="{CCF57805-2741-4C93-98B7-D361D0EE1D76}"/>
+    <hyperlink ref="C27" r:id="rId11" xr:uid="{1AD065D4-1978-475F-AE7F-D0045B9251B4}"/>
+    <hyperlink ref="C3" r:id="rId12" xr:uid="{E821A63E-EBB2-4817-A8B2-87D71FC5D7D5}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId13"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDB43275-BEC1-4DF6-B56D-B5F180583A40}">
   <dimension ref="A2:F70"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="13.9"/>
@@ -1717,61 +1953,61 @@
     <row r="2" spans="1:6" ht="15">
       <c r="A2" s="3"/>
       <c r="B2" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="B3" s="43" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="B4" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="B5" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="B7" s="43" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="B8" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="B9" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="C9" s="13" t="s">
         <v>129</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15">
       <c r="A11" s="3"/>
       <c r="B11" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C11" s="15"/>
       <c r="D11" s="15"/>
@@ -1781,10 +2017,10 @@
     <row r="12" spans="1:6">
       <c r="A12" s="7"/>
       <c r="B12" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C12" s="16" t="s">
         <v>87</v>
-      </c>
-      <c r="C12" s="16" t="s">
-        <v>88</v>
       </c>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
@@ -1798,10 +2034,10 @@
     <row r="14" spans="1:6">
       <c r="A14" s="7"/>
       <c r="B14" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
@@ -1839,86 +2075,86 @@
     <row r="19" spans="1:3" ht="15">
       <c r="A19" s="3"/>
       <c r="B19" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="B20" s="43" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="B21" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="B22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="B23" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="B24" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="B26" s="43" t="s">
+        <v>116</v>
+      </c>
+      <c r="C26" s="13" t="s">
         <v>117</v>
-      </c>
-      <c r="C26" s="13" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="B27" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="B28" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="B29" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="B30" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="15">
       <c r="A32" s="3"/>
       <c r="B32" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="B33" s="12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -1926,27 +2162,27 @@
     </row>
     <row r="35" spans="1:6">
       <c r="B35" s="43" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="B36" s="43" t="s">
+        <v>130</v>
+      </c>
+      <c r="C36" s="13" t="s">
         <v>131</v>
-      </c>
-      <c r="C36" s="13" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="15">
       <c r="A38" s="3"/>
       <c r="B38" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="15">
@@ -1969,7 +2205,7 @@
       <c r="C41" s="9"/>
       <c r="D41" s="8"/>
       <c r="E41" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -2449,11 +2685,11 @@
         <v>7</v>
       </c>
       <c r="C66" s="34" t="e">
-        <f>IF(Macro!#REF!&gt;=3%, "Hot - High", IF(Macro!#REF!&lt;=1.5%, "Cold - Low", "Mixed - Dormant"))</f>
+        <f>IF(Market_Yield!#REF!&gt;=3%, "Hot - High", IF(Market_Yield!#REF!&lt;=1.5%, "Cold - Low", "Mixed - Dormant"))</f>
         <v>#REF!</v>
       </c>
       <c r="D66" s="34" t="e">
-        <f>IF(Macro!#REF!&gt;=3%, "Hot - High", IF(Macro!#REF!&lt;=1.5%, "Cold - Low", "Mixed - Dormant"))</f>
+        <f>IF(Market_Yield!#REF!&gt;=3%, "Hot - High", IF(Market_Yield!#REF!&lt;=1.5%, "Cold - Low", "Mixed - Dormant"))</f>
         <v>#REF!</v>
       </c>
       <c r="E66" s="23" t="e">
@@ -2533,11 +2769,11 @@
         <v>3</v>
       </c>
       <c r="C70" s="35" t="e">
-        <f>Macro!#REF!*(1+E70)</f>
+        <f>Market_Yield!#REF!*(1+E70)</f>
         <v>#REF!</v>
       </c>
       <c r="D70" s="35" t="e">
-        <f>Macro!#REF!*(1+F70)</f>
+        <f>Market_Yield!#REF!*(1+F70)</f>
         <v>#REF!</v>
       </c>
       <c r="E70" s="24" t="e">
@@ -2634,322 +2870,171 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54B06D35-F870-9847-BA9B-1E2F9FFBE611}">
-  <dimension ref="B2:C15"/>
+  <dimension ref="A2:C16"/>
   <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="13.9"/>
   <cols>
+    <col min="1" max="1" width="2.46484375" customWidth="1"/>
     <col min="2" max="2" width="24.6640625" customWidth="1"/>
     <col min="3" max="3" width="51" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3">
-      <c r="B2" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="C2" s="13" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="4" spans="2:3">
-      <c r="B4" s="12" t="s">
+    <row r="2" spans="1:3" ht="15">
+      <c r="A2" s="3"/>
+      <c r="B2" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="B3" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="B5" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C5" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="C4" s="13" t="s">
+    </row>
+    <row r="7" spans="1:3">
+      <c r="B7" s="12" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="B8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="B9" s="46" t="s">
+        <v>155</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="B10" s="46" t="s">
+        <v>154</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="B12" s="14" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="B13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="B15" s="12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="B16" t="s">
+        <v>78</v>
+      </c>
+      <c r="C16" s="13" t="s">
         <v>77</v>
-      </c>
-    </row>
-    <row r="6" spans="2:3">
-      <c r="B6" s="12" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="7" spans="2:3">
-      <c r="B7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="8" spans="2:3">
-      <c r="B8" s="46" t="s">
-        <v>157</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="9" spans="2:3">
-      <c r="B9" s="46" t="s">
-        <v>156</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="11" spans="2:3">
-      <c r="B11" s="14" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="12" spans="2:3">
-      <c r="B12" t="s">
-        <v>73</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="14" spans="2:3">
-      <c r="B14" s="12" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="15" spans="2:3">
-      <c r="B15" t="s">
-        <v>79</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>78</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="11" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="C7" r:id="rId1" xr:uid="{BD2948D7-96D9-264F-B0D8-E6D98C96444B}"/>
-    <hyperlink ref="C12" r:id="rId2" xr:uid="{00B87B71-2B64-7648-8C06-ED4B13CF1CAC}"/>
-    <hyperlink ref="C4" r:id="rId3" xr:uid="{2EBA3D15-8A74-E446-A2A5-3050276DAEF0}"/>
-    <hyperlink ref="C15" r:id="rId4" xr:uid="{C49E8DEC-BC7E-F34D-949B-76A17DA7B973}"/>
-    <hyperlink ref="C2" r:id="rId5" xr:uid="{18F23401-4E80-A24F-B5F3-B57C2EA041C5}"/>
-    <hyperlink ref="C9" r:id="rId6" xr:uid="{5B060AD5-B453-475A-AE85-6F08E6150FB3}"/>
-    <hyperlink ref="C8" r:id="rId7" xr:uid="{55E080AE-5E7C-47FD-A5AD-AADFA910A2B5}"/>
+    <hyperlink ref="C8" r:id="rId1" xr:uid="{BD2948D7-96D9-264F-B0D8-E6D98C96444B}"/>
+    <hyperlink ref="C13" r:id="rId2" xr:uid="{00B87B71-2B64-7648-8C06-ED4B13CF1CAC}"/>
+    <hyperlink ref="C5" r:id="rId3" xr:uid="{2EBA3D15-8A74-E446-A2A5-3050276DAEF0}"/>
+    <hyperlink ref="C16" r:id="rId4" xr:uid="{C49E8DEC-BC7E-F34D-949B-76A17DA7B973}"/>
+    <hyperlink ref="C3" r:id="rId5" xr:uid="{18F23401-4E80-A24F-B5F3-B57C2EA041C5}"/>
+    <hyperlink ref="C10" r:id="rId6" xr:uid="{5B060AD5-B453-475A-AE85-6F08E6150FB3}"/>
+    <hyperlink ref="C9" r:id="rId7" xr:uid="{55E080AE-5E7C-47FD-A5AD-AADFA910A2B5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CEBDF31-D93E-6148-9E83-2491198D4CE1}">
-  <dimension ref="B2:D13"/>
+  <dimension ref="A2:D14"/>
   <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="13.9"/>
   <cols>
+    <col min="1" max="1" width="2.46484375" customWidth="1"/>
     <col min="2" max="2" width="18.46484375" customWidth="1"/>
     <col min="3" max="3" width="38.6640625" customWidth="1"/>
     <col min="4" max="4" width="34.46484375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4">
-      <c r="C2" s="1" t="s">
+    <row r="2" spans="1:4" ht="15">
+      <c r="A2" s="3"/>
+      <c r="B2" s="2" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="C3" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="3" spans="2:4">
-      <c r="B3" t="s">
+    </row>
+    <row r="4" spans="1:4">
+      <c r="B4" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C4" s="13" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="B6" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="B8" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="B10" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="5" spans="2:4">
-      <c r="B5" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4">
-      <c r="B7" t="s">
+    <row r="12" spans="1:4">
+      <c r="B12" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="9" spans="2:4">
-      <c r="B9" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="11" spans="2:4">
-      <c r="B11" t="s">
+    <row r="14" spans="1:4">
+      <c r="B14" t="s">
         <v>104</v>
-      </c>
-    </row>
-    <row r="13" spans="2:4">
-      <c r="B13" t="s">
-        <v>105</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="11" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="C3" r:id="rId1" xr:uid="{D5EB599C-0AC8-C945-97CD-4616A9DA5B5A}"/>
+    <hyperlink ref="C4" r:id="rId1" xr:uid="{D5EB599C-0AC8-C945-97CD-4616A9DA5B5A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B29DA212-C2AF-4D3E-9C01-BCAB145BF990}">
-  <dimension ref="A2:C27"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="13.9"/>
-  <cols>
-    <col min="1" max="1" width="2.46484375" style="7" customWidth="1"/>
-    <col min="2" max="2" width="41.796875" style="7" customWidth="1"/>
-    <col min="3" max="6" width="20.796875" style="7" customWidth="1"/>
-    <col min="7" max="16384" width="8.796875" style="7"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:3" ht="15">
-      <c r="A2" s="3"/>
-      <c r="B2" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="C2" s="16" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="B3" s="43" t="s">
-        <v>114</v>
-      </c>
-      <c r="C3" s="16" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="B4" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="B5" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="B7" s="43" t="s">
-        <v>111</v>
-      </c>
-      <c r="C7" s="16"/>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="B8" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="B9" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="C9" s="16" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="B11" s="43" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="B12" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="C12" s="16" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="B14" s="43" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="B15" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="C15" s="16" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3">
-      <c r="B17" s="43" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3">
-      <c r="B18" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="C18" s="16" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="20" spans="2:3">
-      <c r="B20" s="43" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="21" spans="2:3">
-      <c r="B21" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="C21" s="16" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="23" spans="2:3">
-      <c r="B23" s="43" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="24" spans="2:3">
-      <c r="B24" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="C24" s="16" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="26" spans="2:3">
-      <c r="B26" s="43" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="27" spans="2:3">
-      <c r="B27" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="C27" s="16" t="s">
-        <v>182</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="11" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="C5" r:id="rId1" xr:uid="{7EA46E5E-057B-48C9-8A0D-B56B623EF344}"/>
-    <hyperlink ref="C4" r:id="rId2" xr:uid="{8FF96C9D-4D1A-4741-A8FC-C93FF0BAEB17}"/>
-    <hyperlink ref="C12" r:id="rId3" xr:uid="{7720DD14-3F75-4F25-8D70-F6180ED9FB8E}"/>
-    <hyperlink ref="C9" r:id="rId4" xr:uid="{24CE27D2-F11F-4C96-99C0-31B5BD7EA483}"/>
-    <hyperlink ref="C18" r:id="rId5" xr:uid="{09648102-1869-492C-87E8-7FC427C0F56E}"/>
-    <hyperlink ref="C15" r:id="rId6" xr:uid="{2EDD765B-40DE-4D2D-9531-556EBBD3F442}"/>
-    <hyperlink ref="C2" r:id="rId7" xr:uid="{7787D8AC-7779-42B9-928B-03FC735FB8BD}"/>
-    <hyperlink ref="C8" r:id="rId8" xr:uid="{BA156D29-558F-489F-A67F-2DF63DB9298F}"/>
-    <hyperlink ref="C21" r:id="rId9" xr:uid="{7654C459-BEF7-4D12-A6F9-A473435AB19D}"/>
-    <hyperlink ref="C24" r:id="rId10" xr:uid="{CCF57805-2741-4C93-98B7-D361D0EE1D76}"/>
-    <hyperlink ref="C27" r:id="rId11" xr:uid="{1AD065D4-1978-475F-AE7F-D0045B9251B4}"/>
-    <hyperlink ref="C3" r:id="rId12" xr:uid="{E821A63E-EBB2-4817-A8B2-87D71FC5D7D5}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId13"/>
-</worksheet>
 </file>
--- a/financial_models/Macro_Monitor.xlsx
+++ b/financial_models/Macro_Monitor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4B82A0B-EDC0-427F-AC2A-3CC082478A84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8E37C37-2678-4587-A60F-3F5D218258A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="196">
   <si>
     <t>China</t>
   </si>
@@ -266,470 +266,470 @@
     <t>https://fred.stlouisfed.org/series/CPALTT01CNM659N</t>
   </si>
   <si>
-    <t>BBB Bond yield</t>
+    <t>https://fred.stlouisfed.org/series/DGS10</t>
+  </si>
+  <si>
+    <t>CN</t>
+  </si>
+  <si>
+    <t>Crude oil</t>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/commodity/crude-oil</t>
+  </si>
+  <si>
+    <t>Energy:</t>
+  </si>
+  <si>
+    <t>Gold</t>
+  </si>
+  <si>
+    <t>Metals:</t>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/commodity/gold</t>
+  </si>
+  <si>
+    <t>All-in-one Dash Board</t>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/commodities</t>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/commodity/wheat</t>
+  </si>
+  <si>
+    <t>Wheat</t>
+  </si>
+  <si>
+    <t>Agricultural:</t>
+  </si>
+  <si>
+    <t>All-in-one Currency Dashboard</t>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/currencies</t>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/china/currency</t>
+  </si>
+  <si>
+    <t>USDCNY</t>
+  </si>
+  <si>
+    <t>All-in-One Growth Rate</t>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/country-list/gdp-growth-rate</t>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/country-list/inflation-rate</t>
+  </si>
+  <si>
+    <t>All-in-One Inflation Rate</t>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/cadcny:cur</t>
+  </si>
+  <si>
+    <t>CADCNY</t>
+  </si>
+  <si>
+    <t>HKDCNY</t>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/hkdcny:cur</t>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/canada/currency</t>
+  </si>
+  <si>
+    <t>USDCAD</t>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/japan/currency</t>
+  </si>
+  <si>
+    <t>USDJAY</t>
+  </si>
+  <si>
+    <t>EURUSD</t>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/euro-area/currency</t>
+  </si>
+  <si>
+    <t>https://hk.centanet.com/CCI/CCI</t>
+  </si>
+  <si>
+    <t>Canada</t>
+  </si>
+  <si>
+    <t>USA</t>
+  </si>
+  <si>
+    <t>UK</t>
+  </si>
+  <si>
+    <t>Australia</t>
+  </si>
+  <si>
+    <t>Residential</t>
+  </si>
+  <si>
+    <t>Commercial</t>
+  </si>
+  <si>
+    <t>Logics - do not delete</t>
+  </si>
+  <si>
+    <t>Economic Indicators</t>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/china/forecast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. China </t>
+  </si>
+  <si>
+    <t>Non-Manufacturing PMI</t>
+  </si>
+  <si>
+    <t>Manufacturing PMI</t>
+  </si>
+  <si>
+    <t>1. US</t>
+  </si>
+  <si>
+    <t>GDP &amp; CPI</t>
+  </si>
+  <si>
+    <t>Balance of Payment</t>
+  </si>
+  <si>
+    <t>2. China</t>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/china/balance-of-trade</t>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/china/current-account</t>
+  </si>
+  <si>
+    <t>Current Account (CA)</t>
+  </si>
+  <si>
+    <t>Capital Account (KA)</t>
+  </si>
+  <si>
+    <t>Financial Account (RA)</t>
+  </si>
+  <si>
+    <t>Net Errors and Ommisions (EA)</t>
+  </si>
+  <si>
+    <t>Leading Indicators</t>
+  </si>
+  <si>
+    <t>https://www.conference-board.org/topics/global-economic-outlook</t>
+  </si>
+  <si>
+    <t>Global Outlook</t>
+  </si>
+  <si>
+    <t>1. US LEI</t>
+  </si>
+  <si>
+    <t>https://en.macromicro.me/collections/25/cn-industry-relative/232/cn-pmi-caixin</t>
+  </si>
+  <si>
+    <t>Non-Manufacturing NMI</t>
+  </si>
+  <si>
+    <t>https://en.macromicro.me/collections/25/cn-industry-relative/233/cn-nmi-caixin</t>
+  </si>
+  <si>
+    <t>2. Global LEI</t>
+  </si>
+  <si>
+    <t>https://www.conference-board.org/topics/business-cycle-indicators</t>
+  </si>
+  <si>
+    <t>https://www.conference-board.org/topics/us-leading-indicators</t>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/united-states/forecast</t>
+  </si>
+  <si>
+    <t>https://en.macromicro.me/collections/8/us-industry-relative/54/ism</t>
+  </si>
+  <si>
+    <t>https://en.macromicro.me/collections/8/us-industry-relative/55/ism-nonmanus</t>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/commodity/crb</t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/series/VIXCLS</t>
+  </si>
+  <si>
+    <t>Sentiment/Volatility</t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/series/CHNB6FATT01CXCUQ</t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/series/CHNB6FARA01CXCUQ</t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/series/CHNB6CATT00CXCUQ</t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/series/FEDFUNDS</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>US 10Y Treasury yield</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>US Fed Fund Rate</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>CN 10Y Government Bond Yield</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/china/interest-rate</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>CN Loan Prime Rate</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/commodity/coal</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Coal</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Natural </t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/commodity/natural-gas</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stock Indices</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>S&amp;P 500</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>3. Canada</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>DJI</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://finance.yahoo.com/quote/%5EDJI/</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://finance.yahoo.com/quote/%5EGSPC/</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Nikkei 225</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>4. Japan</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/canada/stock-market</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>TSX</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.etnet.com.hk/www/tc/stocks/indexes_chart_interactive.php?subtype=HIS</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.sgx.com/indices/products/sti</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>STI</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>5. Singapore</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/japan/stock-market</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/stocks</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/china/stock-market</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>6. Australia</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/australia/stock-market</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>ASX</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>7. India</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/india/stock-market</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sensex</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/united-kingdom/stock-market</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>8. Britain</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>FTSE 100</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shanghai Composite Index</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hang Seng Index</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/united-states/stock-market</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Market Yields:</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Notes</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Forex</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Valuation Model Assumptions</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>CRB Commodity Index</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Commodities</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Real Estate</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Target Annual Return</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base Cost of Equity</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>China</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>HK</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/hong-kong/government-bond-yield</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>HK 10Y Government Bond Yield</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/hong-kong/bank-lending-rate</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>HK Prime Lending Rate</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/series/DPRIME</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bank Prime Loan Rate</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prime Rate</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Risk Premium</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Riskfree rate</t>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>https://tradingeconomics.com/china/government-bond-yield</t>
-  </si>
-  <si>
-    <t>https://iftp.chinamoney.com.cn/chinese/scsjzqxx/</t>
-  </si>
-  <si>
-    <t>https://yield.chinabond.com.cn/cbweb-mn/yield_main?locale=en_US</t>
-  </si>
-  <si>
-    <t>CN Onshore BBB- Bond yield</t>
-  </si>
-  <si>
-    <t>CN Offshore BBB- Bond yield</t>
-  </si>
-  <si>
-    <t>https://fred.stlouisfed.org/series/DGS10</t>
-  </si>
-  <si>
-    <t>CN</t>
-  </si>
-  <si>
-    <t>Crude oil</t>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/commodity/crude-oil</t>
-  </si>
-  <si>
-    <t>Energy:</t>
-  </si>
-  <si>
-    <t>Gold</t>
-  </si>
-  <si>
-    <t>Metals:</t>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/commodity/gold</t>
-  </si>
-  <si>
-    <t>All-in-one Dash Board</t>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/commodities</t>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/commodity/wheat</t>
-  </si>
-  <si>
-    <t>Wheat</t>
-  </si>
-  <si>
-    <t>Agricultural:</t>
-  </si>
-  <si>
-    <t>All-in-one Currency Dashboard</t>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/currencies</t>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/china/currency</t>
-  </si>
-  <si>
-    <t>USDCNY</t>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>All-in-One Bond Prices</t>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>https://tradingeconomics.com/bonds</t>
-  </si>
-  <si>
-    <t>All-in-One Growth Rate</t>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/country-list/gdp-growth-rate</t>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/country-list/inflation-rate</t>
-  </si>
-  <si>
-    <t>All-in-One Inflation Rate</t>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/cadcny:cur</t>
-  </si>
-  <si>
-    <t>CADCNY</t>
-  </si>
-  <si>
-    <t>HKDCNY</t>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/hkdcny:cur</t>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/canada/currency</t>
-  </si>
-  <si>
-    <t>USDCAD</t>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/japan/currency</t>
-  </si>
-  <si>
-    <t>USDJAY</t>
-  </si>
-  <si>
-    <t>EURUSD</t>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/euro-area/currency</t>
-  </si>
-  <si>
-    <t>https://hk.centanet.com/CCI/CCI</t>
-  </si>
-  <si>
-    <t>Canada</t>
-  </si>
-  <si>
-    <t>USA</t>
-  </si>
-  <si>
-    <t>UK</t>
-  </si>
-  <si>
-    <t>Australia</t>
-  </si>
-  <si>
-    <t>Residential</t>
-  </si>
-  <si>
-    <t>Commercial</t>
-  </si>
-  <si>
-    <t>Logics - do not delete</t>
-  </si>
-  <si>
-    <t>Economic Indicators</t>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/china/forecast</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. China </t>
-  </si>
-  <si>
-    <t>Non-Manufacturing PMI</t>
-  </si>
-  <si>
-    <t>Manufacturing PMI</t>
-  </si>
-  <si>
-    <t>1. US</t>
-  </si>
-  <si>
-    <t>GDP &amp; CPI</t>
-  </si>
-  <si>
-    <t>Balance of Payment</t>
-  </si>
-  <si>
-    <t>2. China</t>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/china/balance-of-trade</t>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/china/current-account</t>
-  </si>
-  <si>
-    <t>Current Account (CA)</t>
-  </si>
-  <si>
-    <t>Capital Account (KA)</t>
-  </si>
-  <si>
-    <t>Financial Account (RA)</t>
-  </si>
-  <si>
-    <t>Net Errors and Ommisions (EA)</t>
-  </si>
-  <si>
-    <t>Leading Indicators</t>
-  </si>
-  <si>
-    <t>https://www.conference-board.org/topics/global-economic-outlook</t>
-  </si>
-  <si>
-    <t>Global Outlook</t>
-  </si>
-  <si>
-    <t>1. US LEI</t>
-  </si>
-  <si>
-    <t>https://en.macromicro.me/collections/25/cn-industry-relative/232/cn-pmi-caixin</t>
-  </si>
-  <si>
-    <t>Non-Manufacturing NMI</t>
-  </si>
-  <si>
-    <t>https://en.macromicro.me/collections/25/cn-industry-relative/233/cn-nmi-caixin</t>
-  </si>
-  <si>
-    <t>2. Global LEI</t>
-  </si>
-  <si>
-    <t>https://www.conference-board.org/topics/business-cycle-indicators</t>
-  </si>
-  <si>
-    <t>https://www.conference-board.org/topics/us-leading-indicators</t>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/united-states/forecast</t>
-  </si>
-  <si>
-    <t>https://en.macromicro.me/collections/8/us-industry-relative/54/ism</t>
-  </si>
-  <si>
-    <t>https://en.macromicro.me/collections/8/us-industry-relative/55/ism-nonmanus</t>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/commodity/crb</t>
-  </si>
-  <si>
-    <t>https://fred.stlouisfed.org/series/VIXCLS</t>
-  </si>
-  <si>
-    <t>Sentiment/Volatility</t>
-  </si>
-  <si>
-    <t>https://fred.stlouisfed.org/series/CHNB6FATT01CXCUQ</t>
-  </si>
-  <si>
-    <t>https://fred.stlouisfed.org/series/CHNB6FARA01CXCUQ</t>
-  </si>
-  <si>
-    <t>https://fred.stlouisfed.org/series/CHNB6CATT00CXCUQ</t>
-  </si>
-  <si>
-    <t>https://fred.stlouisfed.org/series/FEDFUNDS</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>US 10Y Treasury yield</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>US Fed Fund Rate</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>US BBB Bond index yield</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>CN 10Y Government Bond Yield</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/china/interest-rate</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>CN Loan Prime Rate</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://fred.stlouisfed.org/series/BAMLC0A2CAAEY</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>US AA Bond index yield</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.spglobal.com/spdji/en/indices/fixed-income/sp-china-corporate-bond-index/#overview</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>CN AA Bond index yield</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/commodity/coal</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>Coal</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Natural </t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/commodity/natural-gas</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>Stock Indices</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>S&amp;P 500</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>3. Canada</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>DJI</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://finance.yahoo.com/quote/%5EDJI/</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://finance.yahoo.com/quote/%5EGSPC/</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>Nikkei 225</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>4. Japan</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/canada/stock-market</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>TSX</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.etnet.com.hk/www/tc/stocks/indexes_chart_interactive.php?subtype=HIS</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.sgx.com/indices/products/sti</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>STI</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>5. Singapore</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/japan/stock-market</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/stocks</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/china/stock-market</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>6. Australia</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/australia/stock-market</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>ASX</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>7. India</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/india/stock-market</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sensex</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/united-kingdom/stock-market</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>8. Britain</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>FTSE 100</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>Shanghai Composite Index</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>Hang Seng Index</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/united-states/stock-market</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>ERP</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bond Premium</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>Equity Cost</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>Nominal Rf rate</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>Market Yields:</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>Notes</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>Forex</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>Valuation Model Assumptions</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>CRB Commodity Index</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>Commodities</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>Real Estate</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>Target Annual Return</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
@@ -843,12 +843,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="5" tint="-0.249977111117893"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="2" tint="-9.9978637043366805E-2"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -869,6 +863,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -998,7 +998,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1032,18 +1032,17 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="10" fontId="13" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="10" fontId="15" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="14" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1106,21 +1105,27 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="176" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="10" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1402,244 +1407,208 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A061C73F-1F33-4614-90A5-D5D9D7C58056}">
-  <dimension ref="A2:G32"/>
+  <dimension ref="A2:E23"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="2.46484375" style="7" customWidth="1"/>
-    <col min="2" max="2" width="47.796875" style="7" customWidth="1"/>
-    <col min="3" max="7" width="15.59765625" style="7" customWidth="1"/>
-    <col min="8" max="16384" width="8.796875" style="7"/>
+    <col min="2" max="2" width="30.19921875" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="15.59765625" style="7" customWidth="1"/>
+    <col min="6" max="16384" width="8.796875" style="7"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:7" ht="15">
+    <row r="2" spans="1:5" ht="15">
       <c r="A2" s="3"/>
       <c r="B2" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="51"/>
-    </row>
-    <row r="3" spans="1:7">
+        <v>176</v>
+      </c>
+      <c r="C2" s="4"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="4"/>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="4"/>
       <c r="B3" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="C3" s="49">
+        <v>180</v>
+      </c>
+      <c r="C3" s="47">
         <v>0.2</v>
       </c>
       <c r="D3" s="50">
         <v>3</v>
       </c>
-      <c r="E3" s="50"/>
-    </row>
-    <row r="4" spans="1:7">
+      <c r="E3" s="48"/>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="4"/>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="4"/>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="4"/>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="C10" s="15" t="s">
+      <c r="B4" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="C4" s="51">
+        <f>MAX(8%,C8:D10)</f>
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="15">
+      <c r="A6" s="3"/>
+      <c r="B6" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="49"/>
+      <c r="E6" s="4"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="C7" s="15" t="s">
+        <v>192</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="B8" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="45">
+        <v>4.2500000000000003E-2</v>
+      </c>
+      <c r="D8" s="45">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="E8" s="46">
+        <f>D8-C8</f>
+        <v>3.2499999999999994E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="B9" s="52" t="s">
+        <v>182</v>
+      </c>
+      <c r="C9" s="45">
+        <v>1.9E-2</v>
+      </c>
+      <c r="D9" s="45">
+        <v>3.1E-2</v>
+      </c>
+      <c r="E9" s="46">
+        <f>D9-C9</f>
+        <v>1.2E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="B10" s="52" t="s">
+        <v>183</v>
+      </c>
+      <c r="C10" s="45">
+        <v>3.4500000000000003E-2</v>
+      </c>
+      <c r="D10" s="45">
+        <v>5.2499999999999998E-2</v>
+      </c>
+      <c r="E10" s="46">
+        <f>D10-C10</f>
+        <v>1.7999999999999995E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="15">
+      <c r="A12" s="3"/>
+      <c r="B12" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C12" s="4"/>
+      <c r="D12" s="49"/>
+      <c r="E12" s="4"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="B13" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="B14" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="B15" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="D10" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="E10" s="15" t="s">
+      <c r="C15" s="16" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="C16" s="16"/>
+    </row>
+    <row r="17" spans="2:3">
+      <c r="B17" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3">
+      <c r="B18" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3">
+      <c r="C19" s="16"/>
+    </row>
+    <row r="20" spans="2:3">
+      <c r="B20" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3">
+      <c r="B21" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="F10" s="15" t="s">
+      <c r="C21" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="G10" s="15" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="15">
-      <c r="A11" s="3"/>
-      <c r="B11" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="C11" s="52"/>
-      <c r="D11" s="53"/>
-      <c r="E11" s="52"/>
-      <c r="F11" s="53"/>
-      <c r="G11" s="51"/>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="B13" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C13" s="47">
-        <v>4.2000000000000003E-2</v>
-      </c>
-      <c r="D13" s="47">
-        <v>5.2299999999999999E-2</v>
-      </c>
-      <c r="E13" s="48">
-        <f>D13-C13</f>
-        <v>1.0299999999999997E-2</v>
-      </c>
-      <c r="F13" s="48">
-        <f>G13-C13</f>
-        <v>3.7999999999999999E-2</v>
-      </c>
-      <c r="G13" s="48">
-        <f>MAX(C13+E13,8%)</f>
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="B14" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="C14" s="47">
-        <v>1.8100000000000002E-2</v>
-      </c>
-      <c r="D14" s="47">
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="E14" s="48">
-        <f>D14-C14</f>
-        <v>4.6899999999999997E-2</v>
-      </c>
-      <c r="F14" s="48">
-        <f>G14-C14</f>
-        <v>8.1900000000000001E-2</v>
-      </c>
-      <c r="G14" s="48">
-        <f>MAX(C14+E14,10%)</f>
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="F17" s="17"/>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="F18" s="17"/>
-    </row>
-    <row r="19" spans="1:7" ht="15">
-      <c r="A19" s="3"/>
-      <c r="B19" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="C19" s="52"/>
-      <c r="D19" s="53"/>
-      <c r="E19" s="52"/>
-      <c r="F19" s="53"/>
-      <c r="G19" s="51"/>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="B20" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="C20" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="F20" s="17"/>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="B21" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="C21" s="16" t="s">
-        <v>142</v>
-      </c>
-      <c r="F21" s="17"/>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="B22" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="C22" s="16" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="B23" s="4" t="s">
-        <v>150</v>
+    </row>
+    <row r="22" spans="2:3">
+      <c r="C22" s="16"/>
+    </row>
+    <row r="23" spans="2:3">
+      <c r="B23" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="B24" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="C24" s="16" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="C25" s="45"/>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="B26" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="C26" s="16" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="B27" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="C27" s="16" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="B28" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C28" s="16" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="B29" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C29" s="16" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="B30" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C30" s="16" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="15">
-      <c r="F32" s="53"/>
-      <c r="G32" s="51"/>
+        <v>195</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="11" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="C30" r:id="rId1" xr:uid="{DB671679-E839-B64A-AD4E-6D8A323DAFC3}"/>
-    <hyperlink ref="C29" r:id="rId2" xr:uid="{9CB8AD70-9E02-9A41-8E3A-990A0C1E81AE}"/>
-    <hyperlink ref="C27" r:id="rId3" xr:uid="{45D5643F-FA1A-3C48-B2D9-4B6082295A37}"/>
-    <hyperlink ref="C22" r:id="rId4" xr:uid="{8FF27AF7-25A6-F443-A0E6-DAC1AFC8FB4A}"/>
-    <hyperlink ref="C20" r:id="rId5" xr:uid="{E414D4D1-755D-2A43-AB81-B4A0517E9107}"/>
-    <hyperlink ref="C21" r:id="rId6" xr:uid="{BD25C893-4B01-48BE-AB6E-FA9F70DB6325}"/>
-    <hyperlink ref="C26" r:id="rId7" xr:uid="{01B23463-056A-45A3-AFE5-8FCBFF68216B}"/>
-    <hyperlink ref="C24" r:id="rId8" display="https://fred.stlouisfed.org/series/BAMLC0A4CBBBEY" xr:uid="{35ACA25B-AF93-B04F-A9DD-9D3D634DC7A6}"/>
-    <hyperlink ref="C23" r:id="rId9" xr:uid="{410CC38F-2D01-4044-AE85-C4E978B37B55}"/>
-    <hyperlink ref="C28" r:id="rId10" location="overview" xr:uid="{85EC9358-C071-4DB7-96C6-D513DABB95B7}"/>
+    <hyperlink ref="C17" r:id="rId1" xr:uid="{45D5643F-FA1A-3C48-B2D9-4B6082295A37}"/>
+    <hyperlink ref="C13" r:id="rId2" xr:uid="{8FF27AF7-25A6-F443-A0E6-DAC1AFC8FB4A}"/>
+    <hyperlink ref="C23" r:id="rId3" xr:uid="{E414D4D1-755D-2A43-AB81-B4A0517E9107}"/>
+    <hyperlink ref="C14" r:id="rId4" xr:uid="{BD25C893-4B01-48BE-AB6E-FA9F70DB6325}"/>
+    <hyperlink ref="C18" r:id="rId5" xr:uid="{01B23463-056A-45A3-AFE5-8FCBFF68216B}"/>
+    <hyperlink ref="C20" r:id="rId6" xr:uid="{CA446899-0FC4-4E1D-9FA6-827A1A2C6101}"/>
+    <hyperlink ref="C21" r:id="rId7" xr:uid="{2A60B260-D4EE-4AB2-B4D5-2C97E9E3A2EB}"/>
+    <hyperlink ref="C15" r:id="rId8" xr:uid="{7EACBB86-54AE-4C08-9D45-813ABBBD2BC8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId11"/>
+  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId9"/>
 </worksheet>
 </file>
 
@@ -1656,19 +1625,19 @@
     <row r="2" spans="1:5" ht="15">
       <c r="A2" s="3"/>
       <c r="B2" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="52"/>
+        <v>175</v>
+      </c>
+      <c r="C2" s="4"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="4"/>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="7"/>
       <c r="B3" s="6" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -1683,10 +1652,10 @@
     <row r="5" spans="1:5">
       <c r="A5" s="7"/>
       <c r="B5" s="6" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
@@ -1694,10 +1663,10 @@
     <row r="6" spans="1:5">
       <c r="A6" s="7"/>
       <c r="B6" s="6" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
@@ -1705,10 +1674,10 @@
     <row r="7" spans="1:5">
       <c r="A7" s="7"/>
       <c r="B7" s="7" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
@@ -1723,10 +1692,10 @@
     <row r="9" spans="1:5">
       <c r="A9" s="7"/>
       <c r="B9" s="7" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
@@ -1734,10 +1703,10 @@
     <row r="10" spans="1:5">
       <c r="A10" s="7"/>
       <c r="B10" s="7" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D10" s="7"/>
       <c r="E10" s="7"/>
@@ -1752,10 +1721,10 @@
     <row r="12" spans="1:5">
       <c r="A12" s="7"/>
       <c r="B12" s="7" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
@@ -1789,134 +1758,134 @@
     <row r="2" spans="1:3" ht="15">
       <c r="A2" s="3"/>
       <c r="B2" s="2" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="C2" s="16" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="B3" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="C3" s="16" t="s">
         <v>172</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="B3" s="43" t="s">
-        <v>113</v>
-      </c>
-      <c r="C3" s="16" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="B4" s="6" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="B5" s="6" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="B7" s="43" t="s">
-        <v>110</v>
+      <c r="B7" s="42" t="s">
+        <v>102</v>
       </c>
       <c r="C7" s="16"/>
     </row>
     <row r="8" spans="1:3">
       <c r="B8" s="6" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="B9" s="6" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="B11" s="43" t="s">
-        <v>159</v>
+      <c r="B11" s="42" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="B12" s="7" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="B14" s="43" t="s">
-        <v>164</v>
+      <c r="B14" s="42" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="B15" s="7" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
     </row>
     <row r="17" spans="2:3">
-      <c r="B17" s="43" t="s">
-        <v>170</v>
+      <c r="B17" s="42" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="18" spans="2:3">
       <c r="B18" s="7" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
     </row>
     <row r="20" spans="2:3">
-      <c r="B20" s="43" t="s">
-        <v>174</v>
+      <c r="B20" s="42" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="21" spans="2:3">
       <c r="B21" s="7" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
     </row>
     <row r="23" spans="2:3">
-      <c r="B23" s="43" t="s">
-        <v>177</v>
+      <c r="B23" s="42" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="24" spans="2:3">
       <c r="B24" s="7" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
     </row>
     <row r="26" spans="2:3">
-      <c r="B26" s="43" t="s">
-        <v>181</v>
+      <c r="B26" s="42" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="27" spans="2:3">
       <c r="B27" s="7" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
     </row>
   </sheetData>
@@ -1953,74 +1922,74 @@
     <row r="2" spans="1:6" ht="15">
       <c r="A2" s="3"/>
       <c r="B2" s="2" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="B3" s="43" t="s">
-        <v>113</v>
+      <c r="B3" s="42" t="s">
+        <v>105</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="B4" s="6" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="B5" s="6" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="B7" s="43" t="s">
-        <v>110</v>
+      <c r="B7" s="42" t="s">
+        <v>102</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="B8" s="6" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="B9" s="6" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15">
       <c r="A11" s="3"/>
       <c r="B11" s="2" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C11" s="15"/>
       <c r="D11" s="15"/>
       <c r="E11" s="15"/>
-      <c r="F11" s="44"/>
+      <c r="F11" s="43"/>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="7"/>
       <c r="B12" s="4" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
@@ -2034,10 +2003,10 @@
     <row r="14" spans="1:6">
       <c r="A14" s="7"/>
       <c r="B14" s="4" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
@@ -2047,7 +2016,7 @@
       <c r="B15" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C15" s="18" t="s">
+      <c r="C15" s="17" t="s">
         <v>55</v>
       </c>
       <c r="E15" s="7"/>
@@ -2058,7 +2027,7 @@
       <c r="B16" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="C16" s="18" t="s">
         <v>60</v>
       </c>
       <c r="E16" s="7"/>
@@ -2068,121 +2037,121 @@
       <c r="B17" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="C17" s="19" t="s">
+      <c r="C17" s="18" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="15">
       <c r="A19" s="3"/>
       <c r="B19" s="2" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
     </row>
     <row r="20" spans="1:3">
-      <c r="B20" s="43" t="s">
-        <v>113</v>
+      <c r="B20" s="42" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="B21" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="B22" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="B23" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="B24" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
     </row>
     <row r="26" spans="1:3">
-      <c r="B26" s="43" t="s">
-        <v>116</v>
+      <c r="B26" s="42" t="s">
+        <v>108</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="B27" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="B28" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="B29" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="B30" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="15">
       <c r="A32" s="3"/>
       <c r="B32" s="2" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="B33" s="12" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="B34" s="6"/>
     </row>
     <row r="35" spans="1:6">
-      <c r="B35" s="43" t="s">
-        <v>126</v>
+      <c r="B35" s="42" t="s">
+        <v>118</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="43" t="s">
-        <v>130</v>
+      <c r="B36" s="42" t="s">
+        <v>122</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="15">
       <c r="A38" s="3"/>
       <c r="B38" s="2" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="15">
@@ -2191,7 +2160,7 @@
         <v>54</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>1</v>
@@ -2199,588 +2168,588 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="4"/>
-      <c r="B41" s="36" t="s">
+      <c r="B41" s="35" t="s">
         <v>53</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="8"/>
       <c r="E41" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="4"/>
-      <c r="B42" s="37" t="s">
+      <c r="B42" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="C42" s="25" t="s">
+      <c r="C42" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="D42" s="25" t="s">
+      <c r="D42" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="E42" s="20">
+      <c r="E42" s="19">
         <f t="shared" ref="E42:F45" si="0">IF(LEFT(C42,1)="H",1,IF(LEFT(C42,1)="C",-1,0))</f>
         <v>-1</v>
       </c>
-      <c r="F42" s="20">
+      <c r="F42" s="19">
         <f t="shared" si="0"/>
         <v>-1</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="4"/>
-      <c r="B43" s="37" t="s">
+      <c r="B43" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="C43" s="26" t="s">
+      <c r="C43" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="D43" s="26" t="s">
+      <c r="D43" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="E43" s="20">
+      <c r="E43" s="19">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F43" s="20">
+      <c r="F43" s="19">
         <f t="shared" si="0"/>
         <v>-1</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="4"/>
-      <c r="B44" s="37" t="s">
+      <c r="B44" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="C44" s="27" t="s">
+      <c r="C44" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="D44" s="27" t="s">
+      <c r="D44" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="E44" s="20">
+      <c r="E44" s="19">
         <f t="shared" si="0"/>
         <v>-1</v>
       </c>
-      <c r="F44" s="20">
+      <c r="F44" s="19">
         <f t="shared" si="0"/>
         <v>-1</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="4"/>
-      <c r="B45" s="38" t="s">
+      <c r="B45" s="37" t="s">
         <v>45</v>
       </c>
-      <c r="C45" s="28" t="s">
+      <c r="C45" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="D45" s="28" t="s">
+      <c r="D45" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="E45" s="20">
+      <c r="E45" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F45" s="20">
+      <c r="F45" s="19">
         <f t="shared" si="0"/>
         <v>-1</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="4"/>
-      <c r="B46" s="39" t="s">
+      <c r="B46" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="C46" s="29" t="str">
+      <c r="C46" s="28" t="str">
         <f>IF(SUM(E42:E45)&gt;=3, "Hot", IF(SUM(E42:E45)&lt;=-3,"Cold", "Mixed"))</f>
         <v>Mixed</v>
       </c>
-      <c r="D46" s="29" t="str">
+      <c r="D46" s="28" t="str">
         <f>IF(SUM(F42:F45)&gt;=3, "Hot", IF(SUM(F42:F45)&lt;=-3,"Cold", "Mixed"))</f>
         <v>Cold</v>
       </c>
-      <c r="E46" s="20">
+      <c r="E46" s="19">
         <f>IF(LEFT(C46,1)="H",2,IF(LEFT(C46,1)="C",-1,0))</f>
         <v>0</v>
       </c>
-      <c r="F46" s="20">
+      <c r="F46" s="19">
         <f>IF(LEFT(D46,1)="H",2,IF(LEFT(D46,1)="C",-1,0))</f>
         <v>-1</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="4"/>
-      <c r="B47" s="37" t="s">
+      <c r="B47" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="C47" s="25" t="s">
+      <c r="C47" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="D47" s="25" t="s">
+      <c r="D47" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="E47" s="20">
+      <c r="E47" s="19">
         <f t="shared" ref="E47:F50" si="1">IF(LEFT(C47,1)="H",1,IF(LEFT(C47,1)="C",-1,0))</f>
         <v>-1</v>
       </c>
-      <c r="F47" s="20">
+      <c r="F47" s="19">
         <f t="shared" si="1"/>
         <v>-1</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="4"/>
-      <c r="B48" s="37" t="s">
+      <c r="B48" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="C48" s="25" t="s">
+      <c r="C48" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="D48" s="25" t="s">
+      <c r="D48" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="E48" s="20">
+      <c r="E48" s="19">
         <f t="shared" si="1"/>
         <v>-1</v>
       </c>
-      <c r="F48" s="20">
+      <c r="F48" s="19">
         <f t="shared" si="1"/>
         <v>-1</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="4"/>
-      <c r="B49" s="37" t="s">
+      <c r="B49" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="C49" s="28" t="s">
+      <c r="C49" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="D49" s="28" t="s">
+      <c r="D49" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="E49" s="20">
+      <c r="E49" s="19">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F49" s="20">
+      <c r="F49" s="19">
         <f t="shared" si="1"/>
         <v>-1</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="4"/>
-      <c r="B50" s="37" t="s">
+      <c r="B50" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="C50" s="28" t="s">
+      <c r="C50" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="D50" s="28" t="s">
+      <c r="D50" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="E50" s="20">
+      <c r="E50" s="19">
         <f t="shared" si="1"/>
         <v>-1</v>
       </c>
-      <c r="F50" s="20">
+      <c r="F50" s="19">
         <f t="shared" si="1"/>
         <v>-1</v>
       </c>
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="4"/>
-      <c r="B51" s="39" t="s">
+      <c r="B51" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="C51" s="30" t="str">
+      <c r="C51" s="29" t="str">
         <f>IF(SUM(E47:E50)&gt;=3, "Hot", IF(SUM(E47:E50)&lt;=-3,"Cold", "Mixed"))</f>
         <v>Cold</v>
       </c>
-      <c r="D51" s="30" t="str">
+      <c r="D51" s="29" t="str">
         <f>IF(SUM(F47:F50)&gt;=3, "Hot", IF(SUM(F47:F50)&lt;=-3,"Cold", "Mixed"))</f>
         <v>Cold</v>
       </c>
-      <c r="E51" s="20">
+      <c r="E51" s="19">
         <f>IF(LEFT(C51,1)="H",2,IF(LEFT(C51,1)="C",-1,0))</f>
         <v>-1</v>
       </c>
-      <c r="F51" s="20">
+      <c r="F51" s="19">
         <f>IF(LEFT(D51,1)="H",2,IF(LEFT(D51,1)="C",-1,0))</f>
         <v>-1</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="27.75">
       <c r="A52" s="4"/>
-      <c r="B52" s="37" t="s">
+      <c r="B52" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="C52" s="25" t="s">
+      <c r="C52" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="D52" s="25" t="s">
+      <c r="D52" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="E52" s="20">
+      <c r="E52" s="19">
         <f t="shared" ref="E52:F55" si="2">IF(LEFT(C52,1)="H",1,IF(LEFT(C52,1)="C",-1,0))</f>
         <v>1</v>
       </c>
-      <c r="F52" s="20">
+      <c r="F52" s="19">
         <f t="shared" si="2"/>
         <v>-1</v>
       </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="4"/>
-      <c r="B53" s="37" t="s">
+      <c r="B53" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="C53" s="25" t="s">
+      <c r="C53" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="D53" s="25" t="s">
+      <c r="D53" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="E53" s="20">
+      <c r="E53" s="19">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F53" s="20">
+      <c r="F53" s="19">
         <f t="shared" si="2"/>
         <v>-1</v>
       </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="4"/>
-      <c r="B54" s="37" t="s">
+      <c r="B54" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="C54" s="25" t="s">
+      <c r="C54" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="D54" s="25" t="s">
+      <c r="D54" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="E54" s="20">
+      <c r="E54" s="19">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F54" s="20">
+      <c r="F54" s="19">
         <f t="shared" si="2"/>
         <v>-1</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="4"/>
-      <c r="B55" s="37" t="s">
+      <c r="B55" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="C55" s="25" t="s">
+      <c r="C55" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="D55" s="25" t="s">
+      <c r="D55" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="E55" s="20">
+      <c r="E55" s="19">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F55" s="20">
+      <c r="F55" s="19">
         <f t="shared" si="2"/>
         <v>-1</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="4"/>
-      <c r="B56" s="39" t="s">
+      <c r="B56" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="C56" s="30" t="str">
+      <c r="C56" s="29" t="str">
         <f>IF(SUM(E52:E55)&gt;=3, "Hot", IF(SUM(E52:E55)&lt;=-3,"Cold", "Mixed"))</f>
         <v>Mixed</v>
       </c>
-      <c r="D56" s="30" t="str">
+      <c r="D56" s="29" t="str">
         <f>IF(SUM(F52:F55)&gt;=3, "Hot", IF(SUM(F52:F55)&lt;=-3,"Cold", "Mixed"))</f>
         <v>Cold</v>
       </c>
-      <c r="E56" s="20">
+      <c r="E56" s="19">
         <f>IF(LEFT(C56,1)="H",2,IF(LEFT(C56,1)="C",-1,0))</f>
         <v>0</v>
       </c>
-      <c r="F56" s="20">
+      <c r="F56" s="19">
         <f>IF(LEFT(D56,1)="H",2,IF(LEFT(D56,1)="C",-1,0))</f>
         <v>-1</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="27.75">
       <c r="A57" s="4"/>
-      <c r="B57" s="37" t="s">
+      <c r="B57" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="C57" s="25" t="s">
+      <c r="C57" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="D57" s="25" t="s">
+      <c r="D57" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="E57" s="20">
+      <c r="E57" s="19">
         <f t="shared" ref="E57:F60" si="3">IF(LEFT(C57,1)="H",1,IF(LEFT(C57,1)="C",-1,0))</f>
         <v>0</v>
       </c>
-      <c r="F57" s="20">
+      <c r="F57" s="19">
         <f t="shared" si="3"/>
         <v>-1</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="27.75">
       <c r="A58" s="4"/>
-      <c r="B58" s="37" t="s">
+      <c r="B58" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="C58" s="25" t="s">
+      <c r="C58" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="D58" s="25" t="s">
+      <c r="D58" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="E58" s="20">
+      <c r="E58" s="19">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F58" s="20">
+      <c r="F58" s="19">
         <f t="shared" si="3"/>
         <v>-1</v>
       </c>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="4"/>
-      <c r="B59" s="37" t="s">
+      <c r="B59" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C59" s="25" t="s">
+      <c r="C59" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="D59" s="25" t="s">
+      <c r="D59" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E59" s="20">
+      <c r="E59" s="19">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="F59" s="20">
+      <c r="F59" s="19">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="27.75">
       <c r="A60" s="4"/>
-      <c r="B60" s="37" t="s">
+      <c r="B60" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="C60" s="25" t="s">
+      <c r="C60" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="D60" s="25" t="s">
+      <c r="D60" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="E60" s="20">
+      <c r="E60" s="19">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F60" s="20">
+      <c r="F60" s="19">
         <f t="shared" si="3"/>
         <v>-1</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="4"/>
-      <c r="B61" s="39" t="s">
+      <c r="B61" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="C61" s="30" t="str">
+      <c r="C61" s="29" t="str">
         <f>IF(SUM(E57:E60)&gt;=3, "Hot", IF(SUM(E57:E60)&lt;=-3,"Cold", "Mixed"))</f>
         <v>Mixed</v>
       </c>
-      <c r="D61" s="30" t="str">
+      <c r="D61" s="29" t="str">
         <f>IF(SUM(F57:F60)&gt;=3, "Hot", IF(SUM(F57:F60)&lt;=-3,"Cold", "Mixed"))</f>
         <v>Cold</v>
       </c>
-      <c r="E61" s="20">
+      <c r="E61" s="19">
         <f>IF(LEFT(C61,1)="H",2,IF(LEFT(C61,1)="C",-1,0))</f>
         <v>0</v>
       </c>
-      <c r="F61" s="20">
+      <c r="F61" s="19">
         <f>IF(LEFT(D61,1)="H",2,IF(LEFT(D61,1)="C",-1,0))</f>
         <v>-1</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="27.75">
       <c r="A62" s="4"/>
-      <c r="B62" s="40" t="s">
+      <c r="B62" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="C62" s="31" t="str">
+      <c r="C62" s="30" t="str">
         <f>IF(OR(E62=4,E62=-4),"In extreme",IF(E62=0,"In equilibrium",IF(OR(E62&gt;0),"Relatively optimistic","Relatively pessimistic")))</f>
         <v>Relatively pessimistic</v>
       </c>
-      <c r="D62" s="31" t="str">
+      <c r="D62" s="30" t="str">
         <f>IF(OR(F62=4,F62=-4),"In extreme",IF(F62=0,"In equilibrium",IF(OR(F62&gt;0),"Relatively optimistic","Relatively pessimistic")))</f>
         <v>In extreme</v>
       </c>
-      <c r="E62" s="21">
+      <c r="E62" s="20">
         <f>SUM(E46,E51,E56,E61)</f>
         <v>-1</v>
       </c>
-      <c r="F62" s="21">
+      <c r="F62" s="20">
         <f>SUM(F46,F51,F56,F61)</f>
         <v>-4</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="4"/>
-      <c r="B63" s="32"/>
-      <c r="C63" s="32"/>
-      <c r="D63" s="32"/>
-      <c r="E63" s="22"/>
-      <c r="F63" s="22"/>
+      <c r="B63" s="31"/>
+      <c r="C63" s="31"/>
+      <c r="D63" s="31"/>
+      <c r="E63" s="21"/>
+      <c r="F63" s="21"/>
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="4"/>
-      <c r="B64" s="41" t="s">
+      <c r="B64" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="C64" s="33" t="s">
+      <c r="C64" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="D64" s="33" t="s">
+      <c r="D64" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="E64" s="23"/>
-      <c r="F64" s="23"/>
+      <c r="E64" s="22"/>
+      <c r="F64" s="22"/>
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="4"/>
-      <c r="B65" s="38" t="s">
+      <c r="B65" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="C65" s="28" t="s">
+      <c r="C65" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="D65" s="28" t="s">
+      <c r="D65" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="E65" s="23">
+      <c r="E65" s="22">
         <f t="shared" ref="E65:F69" si="4">IF(LEFT(C65,1)="H",2,IF(LEFT(C65,1)="C",0,1))</f>
         <v>2</v>
       </c>
-      <c r="F65" s="23">
+      <c r="F65" s="22">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:6">
-      <c r="B66" s="38" t="s">
+      <c r="B66" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="C66" s="34" t="e">
+      <c r="C66" s="33" t="e">
         <f>IF(Market_Yield!#REF!&gt;=3%, "Hot - High", IF(Market_Yield!#REF!&lt;=1.5%, "Cold - Low", "Mixed - Dormant"))</f>
         <v>#REF!</v>
       </c>
-      <c r="D66" s="34" t="e">
+      <c r="D66" s="33" t="e">
         <f>IF(Market_Yield!#REF!&gt;=3%, "Hot - High", IF(Market_Yield!#REF!&lt;=1.5%, "Cold - Low", "Mixed - Dormant"))</f>
         <v>#REF!</v>
       </c>
-      <c r="E66" s="23" t="e">
+      <c r="E66" s="22" t="e">
         <f t="shared" si="4"/>
         <v>#REF!</v>
       </c>
-      <c r="F66" s="23" t="e">
+      <c r="F66" s="22" t="e">
         <f t="shared" si="4"/>
         <v>#REF!</v>
       </c>
     </row>
     <row r="67" spans="1:6">
-      <c r="B67" s="38" t="s">
+      <c r="B67" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="C67" s="34" t="str">
+      <c r="C67" s="33" t="str">
         <f>C43</f>
         <v>Hot - Positive</v>
       </c>
-      <c r="D67" s="34" t="str">
+      <c r="D67" s="33" t="str">
         <f>D43</f>
         <v>Cold - Negative</v>
       </c>
-      <c r="E67" s="23">
+      <c r="E67" s="22">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="F67" s="23">
+      <c r="F67" s="22">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:6">
-      <c r="B68" s="38" t="s">
+      <c r="B68" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="C68" s="34" t="str">
+      <c r="C68" s="33" t="str">
         <f>C49</f>
         <v>Mixed</v>
       </c>
-      <c r="D68" s="34" t="str">
+      <c r="D68" s="33" t="str">
         <f>D49</f>
         <v>Cold - High</v>
       </c>
-      <c r="E68" s="23">
+      <c r="E68" s="22">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="F68" s="23">
+      <c r="F68" s="22">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="38" t="s">
+      <c r="B69" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="C69" s="34" t="str">
+      <c r="C69" s="33" t="str">
         <f>C50</f>
         <v>Cold - Wide</v>
       </c>
-      <c r="D69" s="34" t="str">
+      <c r="D69" s="33" t="str">
         <f>D50</f>
         <v>Cold - Wide</v>
       </c>
-      <c r="E69" s="23">
+      <c r="E69" s="22">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F69" s="23">
+      <c r="F69" s="22">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:6">
-      <c r="B70" s="42" t="s">
+      <c r="B70" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="C70" s="35" t="e">
+      <c r="C70" s="34" t="e">
         <f>Market_Yield!#REF!*(1+E70)</f>
         <v>#REF!</v>
       </c>
-      <c r="D70" s="35" t="e">
+      <c r="D70" s="34" t="e">
         <f>Market_Yield!#REF!*(1+F70)</f>
         <v>#REF!</v>
       </c>
-      <c r="E70" s="24" t="e">
+      <c r="E70" s="23" t="e">
         <f>SUM(E65:E69)/10</f>
         <v>#REF!</v>
       </c>
-      <c r="F70" s="24" t="e">
+      <c r="F70" s="23" t="e">
         <f>SUM(F65:F69)/10</f>
         <v>#REF!</v>
       </c>
@@ -2883,78 +2852,78 @@
     <row r="2" spans="1:3" ht="15">
       <c r="A2" s="3"/>
       <c r="B2" s="2" t="s">
-        <v>195</v>
+        <v>178</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="B3" s="12" t="s">
-        <v>194</v>
+        <v>177</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="B5" s="12" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="B7" s="12" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="B8" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="B9" s="46" t="s">
-        <v>155</v>
+      <c r="B9" s="44" t="s">
+        <v>142</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="B10" s="46" t="s">
-        <v>154</v>
+      <c r="B10" s="44" t="s">
+        <v>141</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="B12" s="14" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="B13" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="B15" s="12" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="B16" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -2986,15 +2955,15 @@
     <row r="2" spans="1:4" ht="15">
       <c r="A2" s="3"/>
       <c r="B2" s="2" t="s">
-        <v>196</v>
+        <v>179</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="C3" s="1" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -3002,7 +2971,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -3012,22 +2981,22 @@
     </row>
     <row r="8" spans="1:4">
       <c r="B8" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="B10" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="B12" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="B14" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/Macro_Monitor.xlsx
+++ b/financial_models/Macro_Monitor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8E37C37-2678-4587-A60F-3F5D218258A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EF4E814-060F-498B-9ECA-D8D8F7647E7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1837" yWindow="1837" windowWidth="12691" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Market_Yield" sheetId="2" r:id="rId1"/>

--- a/financial_models/Macro_Monitor.xlsx
+++ b/financial_models/Macro_Monitor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EF4E814-060F-498B-9ECA-D8D8F7647E7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E2E20E5-03AD-42F5-A9F6-125A0E0F7E2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1837" yWindow="1837" windowWidth="12691" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1103" yWindow="1103" windowWidth="12690" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Market_Yield" sheetId="2" r:id="rId1"/>

--- a/financial_models/Macro_Monitor.xlsx
+++ b/financial_models/Macro_Monitor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E2E20E5-03AD-42F5-A9F6-125A0E0F7E2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BF90FB8-9E87-423E-B8E5-87144A9B79CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1103" yWindow="1103" windowWidth="12690" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Market_Yield" sheetId="2" r:id="rId1"/>
@@ -1473,14 +1473,14 @@
         <v>1</v>
       </c>
       <c r="C8" s="45">
-        <v>4.2500000000000003E-2</v>
+        <v>4.24E-2</v>
       </c>
       <c r="D8" s="45">
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="E8" s="46">
         <f>D8-C8</f>
-        <v>3.2499999999999994E-2</v>
+        <v>3.2599999999999997E-2</v>
       </c>
     </row>
     <row r="9" spans="1:5">

--- a/financial_models/Macro_Monitor.xlsx
+++ b/financial_models/Macro_Monitor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BF90FB8-9E87-423E-B8E5-87144A9B79CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72EE935F-B96E-44B8-A0F4-ED7B1DEDE7D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1473,14 +1473,14 @@
         <v>1</v>
       </c>
       <c r="C8" s="45">
-        <v>4.24E-2</v>
+        <v>4.2500000000000003E-2</v>
       </c>
       <c r="D8" s="45">
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="E8" s="46">
         <f>D8-C8</f>
-        <v>3.2599999999999997E-2</v>
+        <v>3.2499999999999994E-2</v>
       </c>
     </row>
     <row r="9" spans="1:5">

--- a/financial_models/Macro_Monitor.xlsx
+++ b/financial_models/Macro_Monitor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72EE935F-B96E-44B8-A0F4-ED7B1DEDE7D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BE33E23-7707-408F-8F21-4F075F8358E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Market_Yield" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="207">
   <si>
     <t>China</t>
   </si>
@@ -730,6 +730,50 @@
   </si>
   <si>
     <t>https://tradingeconomics.com/bonds</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Benchmarket Return:</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://awealthofcommonsense.com/2025/01/historical-returns-for-stocks-bonds-cash-real-estate-and-gold/</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Historical Returns</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stocks</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Small caps</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bonds</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cash</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gold</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Real estate</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>US (1928-2024)</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Benchmark for stocks</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
@@ -911,7 +955,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -993,12 +1037,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1106,10 +1165,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1123,9 +1178,20 @@
     <xf numFmtId="10" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="10" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1407,7 +1473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A061C73F-1F33-4614-90A5-D5D9D7C58056}">
-  <dimension ref="A2:E23"/>
+  <dimension ref="A2:E36"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="2.46484375" style="7" customWidth="1"/>
@@ -1422,7 +1488,7 @@
         <v>176</v>
       </c>
       <c r="C2" s="4"/>
-      <c r="D2" s="49"/>
+      <c r="D2" s="47"/>
       <c r="E2" s="4"/>
     </row>
     <row r="3" spans="1:5">
@@ -1430,20 +1496,20 @@
       <c r="B3" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="C3" s="47">
+      <c r="C3" s="45">
         <v>0.2</v>
       </c>
-      <c r="D3" s="50">
+      <c r="D3" s="48">
         <v>3</v>
       </c>
-      <c r="E3" s="48"/>
+      <c r="E3" s="46"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="4"/>
       <c r="B4" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="C4" s="51">
+      <c r="C4" s="49">
         <f>MAX(8%,C8:D10)</f>
         <v>0.08</v>
       </c>
@@ -1454,7 +1520,7 @@
         <v>173</v>
       </c>
       <c r="C6" s="4"/>
-      <c r="D6" s="49"/>
+      <c r="D6" s="47"/>
       <c r="E6" s="4"/>
     </row>
     <row r="7" spans="1:5">
@@ -1469,46 +1535,46 @@
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="B8" s="52" t="s">
+      <c r="B8" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="45">
+      <c r="C8" s="51">
         <v>4.2500000000000003E-2</v>
       </c>
-      <c r="D8" s="45">
+      <c r="D8" s="51">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="E8" s="46">
+      <c r="E8" s="52">
         <f>D8-C8</f>
         <v>3.2499999999999994E-2</v>
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="B9" s="52" t="s">
+      <c r="B9" s="50" t="s">
         <v>182</v>
       </c>
-      <c r="C9" s="45">
+      <c r="C9" s="51">
         <v>1.9E-2</v>
       </c>
-      <c r="D9" s="45">
+      <c r="D9" s="51">
         <v>3.1E-2</v>
       </c>
-      <c r="E9" s="46">
+      <c r="E9" s="52">
         <f>D9-C9</f>
         <v>1.2E-2</v>
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="B10" s="52" t="s">
+      <c r="B10" s="50" t="s">
         <v>183</v>
       </c>
-      <c r="C10" s="45">
+      <c r="C10" s="51">
         <v>3.4500000000000003E-2</v>
       </c>
-      <c r="D10" s="45">
+      <c r="D10" s="51">
         <v>5.2499999999999998E-2</v>
       </c>
-      <c r="E10" s="46">
+      <c r="E10" s="52">
         <f>D10-C10</f>
         <v>1.7999999999999995E-2</v>
       </c>
@@ -1516,99 +1582,176 @@
     <row r="12" spans="1:5" ht="15">
       <c r="A12" s="3"/>
       <c r="B12" s="2" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="C13" s="15" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="B14" s="53" t="s">
+        <v>199</v>
+      </c>
+      <c r="C14" s="51">
+        <v>9.9400000000000002E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="B15" s="53" t="s">
+        <v>200</v>
+      </c>
+      <c r="C15" s="51">
+        <v>0.1174</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="B16" s="53" t="s">
+        <v>201</v>
+      </c>
+      <c r="C16" s="51">
+        <v>3.4500000000000003E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="B17" s="53" t="s">
+        <v>202</v>
+      </c>
+      <c r="C17" s="51">
+        <v>3.3099999999999997E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="B18" s="53" t="s">
+        <v>204</v>
+      </c>
+      <c r="C18" s="51">
+        <v>4.2299999999999997E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="B19" s="53" t="s">
+        <v>203</v>
+      </c>
+      <c r="C19" s="51">
+        <v>5.1200000000000002E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="B20" s="54" t="s">
+        <v>206</v>
+      </c>
+      <c r="C20" s="55">
+        <f>MAX(C4,C14:C19)</f>
+        <v>0.1174</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="15">
+      <c r="A23" s="3"/>
+      <c r="B23" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="49"/>
-      <c r="E12" s="4"/>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="B13" s="4" t="s">
+      <c r="C23" s="4"/>
+      <c r="D23" s="47"/>
+      <c r="E23" s="4"/>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="B24" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C24" s="16" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
-      <c r="B14" s="7" t="s">
+    <row r="25" spans="1:5">
+      <c r="B25" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C25" s="16" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
-      <c r="B15" s="7" t="s">
+    <row r="26" spans="1:5">
+      <c r="B26" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="C26" s="16" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
-      <c r="C16" s="16"/>
-    </row>
-    <row r="17" spans="2:3">
-      <c r="B17" s="7" t="s">
+    <row r="27" spans="1:5">
+      <c r="C27" s="16"/>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="B28" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="C28" s="16" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="18" spans="2:3">
-      <c r="B18" s="7" t="s">
+    <row r="29" spans="1:5">
+      <c r="B29" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="C18" s="16" t="s">
+      <c r="C29" s="16" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="19" spans="2:3">
-      <c r="C19" s="16"/>
-    </row>
-    <row r="20" spans="2:3">
-      <c r="B20" s="7" t="s">
+    <row r="30" spans="1:5">
+      <c r="C30" s="16"/>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="B31" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="C20" s="16" t="s">
+      <c r="C31" s="16" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="21" spans="2:3">
-      <c r="B21" s="7" t="s">
+    <row r="32" spans="1:5">
+      <c r="B32" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="C21" s="16" t="s">
+      <c r="C32" s="16" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="22" spans="2:3">
-      <c r="C22" s="16"/>
-    </row>
-    <row r="23" spans="2:3">
-      <c r="B23" s="7" t="s">
+    <row r="33" spans="2:3">
+      <c r="C33" s="16"/>
+    </row>
+    <row r="34" spans="2:3">
+      <c r="B34" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="C23" s="16" t="s">
+      <c r="C34" s="16" t="s">
         <v>195</v>
+      </c>
+    </row>
+    <row r="36" spans="2:3">
+      <c r="B36" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="C36" s="16" t="s">
+        <v>197</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="11" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="C17" r:id="rId1" xr:uid="{45D5643F-FA1A-3C48-B2D9-4B6082295A37}"/>
-    <hyperlink ref="C13" r:id="rId2" xr:uid="{8FF27AF7-25A6-F443-A0E6-DAC1AFC8FB4A}"/>
-    <hyperlink ref="C23" r:id="rId3" xr:uid="{E414D4D1-755D-2A43-AB81-B4A0517E9107}"/>
-    <hyperlink ref="C14" r:id="rId4" xr:uid="{BD25C893-4B01-48BE-AB6E-FA9F70DB6325}"/>
-    <hyperlink ref="C18" r:id="rId5" xr:uid="{01B23463-056A-45A3-AFE5-8FCBFF68216B}"/>
-    <hyperlink ref="C20" r:id="rId6" xr:uid="{CA446899-0FC4-4E1D-9FA6-827A1A2C6101}"/>
-    <hyperlink ref="C21" r:id="rId7" xr:uid="{2A60B260-D4EE-4AB2-B4D5-2C97E9E3A2EB}"/>
-    <hyperlink ref="C15" r:id="rId8" xr:uid="{7EACBB86-54AE-4C08-9D45-813ABBBD2BC8}"/>
+    <hyperlink ref="C28" r:id="rId1" xr:uid="{45D5643F-FA1A-3C48-B2D9-4B6082295A37}"/>
+    <hyperlink ref="C24" r:id="rId2" xr:uid="{8FF27AF7-25A6-F443-A0E6-DAC1AFC8FB4A}"/>
+    <hyperlink ref="C34" r:id="rId3" xr:uid="{E414D4D1-755D-2A43-AB81-B4A0517E9107}"/>
+    <hyperlink ref="C25" r:id="rId4" xr:uid="{BD25C893-4B01-48BE-AB6E-FA9F70DB6325}"/>
+    <hyperlink ref="C29" r:id="rId5" xr:uid="{01B23463-056A-45A3-AFE5-8FCBFF68216B}"/>
+    <hyperlink ref="C31" r:id="rId6" xr:uid="{CA446899-0FC4-4E1D-9FA6-827A1A2C6101}"/>
+    <hyperlink ref="C32" r:id="rId7" xr:uid="{2A60B260-D4EE-4AB2-B4D5-2C97E9E3A2EB}"/>
+    <hyperlink ref="C26" r:id="rId8" xr:uid="{7EACBB86-54AE-4C08-9D45-813ABBBD2BC8}"/>
+    <hyperlink ref="C36" r:id="rId9" xr:uid="{30137619-E054-41EB-9359-F9138F1700F2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId9"/>
+  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId10"/>
 </worksheet>
 </file>
 
@@ -1628,7 +1771,7 @@
         <v>175</v>
       </c>
       <c r="C2" s="4"/>
-      <c r="D2" s="49"/>
+      <c r="D2" s="47"/>
       <c r="E2" s="4"/>
     </row>
     <row r="3" spans="1:5">

--- a/financial_models/Macro_Monitor.xlsx
+++ b/financial_models/Macro_Monitor.xlsx
@@ -1,24 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BE33E23-7707-408F-8F21-4F075F8358E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D0397B3-B2D9-424F-876C-AC256E6A8D47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Market_Yield" sheetId="2" r:id="rId1"/>
+    <sheet name="Framework" sheetId="10" r:id="rId1"/>
     <sheet name="Forex" sheetId="9" r:id="rId2"/>
     <sheet name="Equity_Indices" sheetId="8" r:id="rId3"/>
     <sheet name="Economies" sheetId="4" r:id="rId4"/>
     <sheet name="Commodities" sheetId="5" r:id="rId5"/>
     <sheet name="Real_Estate" sheetId="6" r:id="rId6"/>
+    <sheet name="Market_Yield" sheetId="2" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="209">
   <si>
     <t>China</t>
   </si>
@@ -641,10 +642,6 @@
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
-    <t>Market Yields:</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
     <t>Notes</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
@@ -653,10 +650,6 @@
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
-    <t>Valuation Model Assumptions</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
     <t>CRB Commodity Index</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
@@ -669,22 +662,6 @@
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
-    <t>Target Annual Return</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Cost of Equity</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>China</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>HK</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
     <t>https://tradingeconomics.com/hong-kong/government-bond-yield</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
@@ -709,18 +686,6 @@
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
-    <t>Prime Rate</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>Risk Premium</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>Riskfree rate</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
     <t>https://tradingeconomics.com/china/government-bond-yield</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
@@ -733,10 +698,6 @@
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
-    <t>Benchmarket Return:</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
     <t>https://awealthofcommonsense.com/2025/01/historical-returns-for-stocks-bonds-cash-real-estate-and-gold/</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
@@ -745,35 +706,212 @@
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
-    <t>Stocks</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>Small caps</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bonds</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>Cash</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>Gold</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>Real estate</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>US (1928-2024)</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>Benchmark for stocks</t>
+    <t>Sector Analysis</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Country/Region Analysis</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Use PEST analysis</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Porter's Five Forces</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Company Analysis</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>5W2H</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>方法</t>
+    </r>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>SWOT</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>第一：了解行业现状</t>
+    </r>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>产业链图</t>
+    </r>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>产业分赃链图</t>
+    </r>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>市场规模预估法实现</t>
+    </r>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>第二：分析行业动能</t>
+    </r>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>外部动能</t>
+    </r>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="DengXian"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>内部动能</t>
+    </r>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="DengXian"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>竞争壁垒</t>
+    </r>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="DengXian"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>行业周期</t>
+    </r>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>第三：推测行业变化</t>
+    </r>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="DengXian"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>竞品分析</t>
+    </r>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>第四：找出行业带给自身的机会</t>
+    </r>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>商业模式画布</t>
+    </r>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
@@ -781,9 +919,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="&quot;for &quot;0&quot; Yrs&quot;"/>
-  </numFmts>
   <fonts count="19">
     <font>
       <sz val="11"/>
@@ -906,15 +1041,17 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Times New Roman"/>
+      <color theme="1"/>
+      <name val="Microsoft YaHei"/>
       <family val="1"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF00B050"/>
-      <name val="Times New Roman"/>
+      <color theme="1"/>
+      <name val="DengXian"/>
       <family val="1"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="7">
@@ -955,7 +1092,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -1037,27 +1174,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1165,33 +1287,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="10" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="176" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="10" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1472,286 +1568,104 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A061C73F-1F33-4614-90A5-D5D9D7C58056}">
-  <dimension ref="A2:E36"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="13.9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEDB0449-8591-42B7-B720-6314A45F3007}">
+  <dimension ref="A2:F15"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="2.46484375" style="7" customWidth="1"/>
-    <col min="2" max="2" width="30.19921875" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="15.59765625" style="7" customWidth="1"/>
-    <col min="6" max="16384" width="8.796875" style="7"/>
+    <col min="1" max="1" width="2.59765625" style="7" customWidth="1"/>
+    <col min="2" max="2" width="37.265625" style="7" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" style="7" customWidth="1"/>
+    <col min="4" max="5" width="18.3984375" style="7" customWidth="1"/>
+    <col min="6" max="6" width="19.73046875" style="7" customWidth="1"/>
+    <col min="7" max="16384" width="9.06640625" style="7"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" ht="15">
+    <row r="2" spans="1:6" ht="15">
       <c r="A2" s="3"/>
       <c r="B2" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="4"/>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="4"/>
-      <c r="B3" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="C3" s="45">
-        <v>0.2</v>
-      </c>
-      <c r="D3" s="48">
-        <v>3</v>
-      </c>
-      <c r="E3" s="46"/>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="4"/>
+        <v>190</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="B4" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="C4" s="49">
-        <f>MAX(8%,C8:D10)</f>
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="15">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15">
       <c r="A6" s="3"/>
       <c r="B6" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="47"/>
-      <c r="E6" s="4"/>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="C7" s="15" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15">
+      <c r="B8" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15">
+      <c r="B9" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15">
+      <c r="B10" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15">
+      <c r="B11" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15">
+      <c r="A13" s="3"/>
+      <c r="B13" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="B14" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="D7" s="15" t="s">
-        <v>190</v>
-      </c>
-      <c r="E7" s="15" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="B8" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="C8" s="51">
-        <v>4.2500000000000003E-2</v>
-      </c>
-      <c r="D8" s="51">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="E8" s="52">
-        <f>D8-C8</f>
-        <v>3.2499999999999994E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="B9" s="50" t="s">
-        <v>182</v>
-      </c>
-      <c r="C9" s="51">
-        <v>1.9E-2</v>
-      </c>
-      <c r="D9" s="51">
-        <v>3.1E-2</v>
-      </c>
-      <c r="E9" s="52">
-        <f>D9-C9</f>
-        <v>1.2E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="B10" s="50" t="s">
-        <v>183</v>
-      </c>
-      <c r="C10" s="51">
-        <v>3.4500000000000003E-2</v>
-      </c>
-      <c r="D10" s="51">
-        <v>5.2499999999999998E-2</v>
-      </c>
-      <c r="E10" s="52">
-        <f>D10-C10</f>
-        <v>1.7999999999999995E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="15">
-      <c r="A12" s="3"/>
-      <c r="B12" s="2" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="C13" s="15" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="B14" s="53" t="s">
-        <v>199</v>
-      </c>
-      <c r="C14" s="51">
-        <v>9.9400000000000002E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="B15" s="53" t="s">
-        <v>200</v>
-      </c>
-      <c r="C15" s="51">
-        <v>0.1174</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="B16" s="53" t="s">
-        <v>201</v>
-      </c>
-      <c r="C16" s="51">
-        <v>3.4500000000000003E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="B17" s="53" t="s">
-        <v>202</v>
-      </c>
-      <c r="C17" s="51">
-        <v>3.3099999999999997E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="B18" s="53" t="s">
-        <v>204</v>
-      </c>
-      <c r="C18" s="51">
-        <v>4.2299999999999997E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="B19" s="53" t="s">
-        <v>203</v>
-      </c>
-      <c r="C19" s="51">
-        <v>5.1200000000000002E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="B20" s="54" t="s">
-        <v>206</v>
-      </c>
-      <c r="C20" s="55">
-        <f>MAX(C4,C14:C19)</f>
-        <v>0.1174</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="15">
-      <c r="A23" s="3"/>
-      <c r="B23" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="C23" s="4"/>
-      <c r="D23" s="47"/>
-      <c r="E23" s="4"/>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="B24" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="C24" s="16" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="B25" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="C25" s="16" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="B26" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="C26" s="16" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="C27" s="16"/>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="B28" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="C28" s="16" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="B29" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="C29" s="16" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="C30" s="16"/>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="B31" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="C31" s="16" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="B32" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="C32" s="16" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="33" spans="2:3">
-      <c r="C33" s="16"/>
-    </row>
-    <row r="34" spans="2:3">
-      <c r="B34" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="C34" s="16" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="36" spans="2:3">
-      <c r="B36" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="C36" s="16" t="s">
-        <v>197</v>
+    </row>
+    <row r="15" spans="1:6" ht="15">
+      <c r="B15" s="7" t="s">
+        <v>208</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="11" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="C28" r:id="rId1" xr:uid="{45D5643F-FA1A-3C48-B2D9-4B6082295A37}"/>
-    <hyperlink ref="C24" r:id="rId2" xr:uid="{8FF27AF7-25A6-F443-A0E6-DAC1AFC8FB4A}"/>
-    <hyperlink ref="C34" r:id="rId3" xr:uid="{E414D4D1-755D-2A43-AB81-B4A0517E9107}"/>
-    <hyperlink ref="C25" r:id="rId4" xr:uid="{BD25C893-4B01-48BE-AB6E-FA9F70DB6325}"/>
-    <hyperlink ref="C29" r:id="rId5" xr:uid="{01B23463-056A-45A3-AFE5-8FCBFF68216B}"/>
-    <hyperlink ref="C31" r:id="rId6" xr:uid="{CA446899-0FC4-4E1D-9FA6-827A1A2C6101}"/>
-    <hyperlink ref="C32" r:id="rId7" xr:uid="{2A60B260-D4EE-4AB2-B4D5-2C97E9E3A2EB}"/>
-    <hyperlink ref="C26" r:id="rId8" xr:uid="{7EACBB86-54AE-4C08-9D45-813ABBBD2BC8}"/>
-    <hyperlink ref="C36" r:id="rId9" xr:uid="{30137619-E054-41EB-9359-F9138F1700F2}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId10"/>
 </worksheet>
 </file>
 
@@ -1768,10 +1682,10 @@
     <row r="2" spans="1:5" ht="15">
       <c r="A2" s="3"/>
       <c r="B2" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C2" s="4"/>
-      <c r="D2" s="47"/>
+      <c r="D2" s="45"/>
       <c r="E2" s="4"/>
     </row>
     <row r="3" spans="1:5">
@@ -2995,12 +2909,12 @@
     <row r="2" spans="1:3" ht="15">
       <c r="A2" s="3"/>
       <c r="B2" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="B3" s="12" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C3" s="13" t="s">
         <v>128</v>
@@ -3098,7 +3012,7 @@
     <row r="2" spans="1:4" ht="15">
       <c r="A2" s="3"/>
       <c r="B2" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -3149,4 +3063,123 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A061C73F-1F33-4614-90A5-D5D9D7C58056}">
+  <dimension ref="A2:E15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="13.9"/>
+  <cols>
+    <col min="1" max="1" width="2.46484375" style="7" customWidth="1"/>
+    <col min="2" max="2" width="30.19921875" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="15.59765625" style="7" customWidth="1"/>
+    <col min="6" max="16384" width="8.796875" style="7"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:5" ht="15">
+      <c r="A2" s="3"/>
+      <c r="B2" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C2" s="4"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="4"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="B3" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="B4" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="B5" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="C6" s="16"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="B7" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="B8" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="C9" s="16"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="B10" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="B11" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="C12" s="16"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="B13" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="B15" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>187</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="11" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="C7" r:id="rId1" xr:uid="{45D5643F-FA1A-3C48-B2D9-4B6082295A37}"/>
+    <hyperlink ref="C3" r:id="rId2" xr:uid="{8FF27AF7-25A6-F443-A0E6-DAC1AFC8FB4A}"/>
+    <hyperlink ref="C13" r:id="rId3" xr:uid="{E414D4D1-755D-2A43-AB81-B4A0517E9107}"/>
+    <hyperlink ref="C4" r:id="rId4" xr:uid="{BD25C893-4B01-48BE-AB6E-FA9F70DB6325}"/>
+    <hyperlink ref="C8" r:id="rId5" xr:uid="{01B23463-056A-45A3-AFE5-8FCBFF68216B}"/>
+    <hyperlink ref="C10" r:id="rId6" xr:uid="{CA446899-0FC4-4E1D-9FA6-827A1A2C6101}"/>
+    <hyperlink ref="C11" r:id="rId7" xr:uid="{2A60B260-D4EE-4AB2-B4D5-2C97E9E3A2EB}"/>
+    <hyperlink ref="C5" r:id="rId8" xr:uid="{7EACBB86-54AE-4C08-9D45-813ABBBD2BC8}"/>
+    <hyperlink ref="C15" r:id="rId9" xr:uid="{30137619-E054-41EB-9359-F9138F1700F2}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId10"/>
+</worksheet>
 </file>
--- a/financial_models/Macro_Monitor.xlsx
+++ b/financial_models/Macro_Monitor.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D0397B3-B2D9-424F-876C-AC256E6A8D47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDF97A56-5D81-4FA1-B103-258ED87A99B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Framework" sheetId="10" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="213">
   <si>
     <t>China</t>
   </si>
@@ -914,6 +914,18 @@
     </r>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
+  <si>
+    <t>Corporate Profit/GDP</t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/graph/?g=fPLQ</t>
+  </si>
+  <si>
+    <t>https://legulegu.com/stockdata/marketcap-gdp</t>
+  </si>
+  <si>
+    <t>Stock Market Cap/GDP</t>
+  </si>
 </sst>
 </file>
 
@@ -923,7 +935,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -931,7 +943,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -995,13 +1007,13 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1029,14 +1041,14 @@
     <font>
       <sz val="11"/>
       <color theme="2" tint="-9.9978637043366805E-2"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1672,14 +1684,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{313BBC5B-4592-4EC9-BE37-C083F15EE9CA}">
   <dimension ref="A2:E12"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="2.46484375" customWidth="1"/>
     <col min="2" max="2" width="27.9296875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" ht="15">
+    <row r="2" spans="1:5" ht="15.4">
       <c r="A2" s="3"/>
       <c r="B2" s="2" t="s">
         <v>174</v>
@@ -1803,7 +1815,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B29DA212-C2AF-4D3E-9C01-BCAB145BF990}">
-  <dimension ref="A2:C27"/>
+  <dimension ref="A2:C29"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="2.46484375" style="7" customWidth="1"/>
@@ -1845,103 +1857,119 @@
         <v>148</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
-      <c r="B7" s="42" t="s">
+    <row r="6" spans="1:3">
+      <c r="B6" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="B8" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="C7" s="16"/>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="B8" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>160</v>
-      </c>
+      <c r="C8" s="16"/>
     </row>
     <row r="9" spans="1:3">
       <c r="B9" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="B10" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C10" s="16" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="B11" s="42" t="s">
+      <c r="B11" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="B13" s="42" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
-      <c r="B12" s="7" t="s">
+    <row r="14" spans="1:3">
+      <c r="B14" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C14" s="16" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
-      <c r="B14" s="42" t="s">
+    <row r="16" spans="1:3">
+      <c r="B16" s="42" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
-      <c r="B15" s="7" t="s">
+    <row r="17" spans="2:3">
+      <c r="B17" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="C17" s="16" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="17" spans="2:3">
-      <c r="B17" s="42" t="s">
+    <row r="19" spans="2:3">
+      <c r="B19" s="42" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="18" spans="2:3">
-      <c r="B18" s="7" t="s">
+    <row r="20" spans="2:3">
+      <c r="B20" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="C18" s="16" t="s">
+      <c r="C20" s="16" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="20" spans="2:3">
-      <c r="B20" s="42" t="s">
+    <row r="22" spans="2:3">
+      <c r="B22" s="42" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="21" spans="2:3">
-      <c r="B21" s="7" t="s">
+    <row r="23" spans="2:3">
+      <c r="B23" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="C21" s="16" t="s">
+      <c r="C23" s="16" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="23" spans="2:3">
-      <c r="B23" s="42" t="s">
+    <row r="25" spans="2:3">
+      <c r="B25" s="42" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="24" spans="2:3">
-      <c r="B24" s="7" t="s">
+    <row r="26" spans="2:3">
+      <c r="B26" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="C24" s="16" t="s">
+      <c r="C26" s="16" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="26" spans="2:3">
-      <c r="B26" s="42" t="s">
+    <row r="28" spans="2:3">
+      <c r="B28" s="42" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="27" spans="2:3">
-      <c r="B27" s="7" t="s">
+    <row r="29" spans="2:3">
+      <c r="B29" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="C27" s="16" t="s">
+      <c r="C29" s="16" t="s">
         <v>167</v>
       </c>
     </row>
@@ -1950,33 +1978,35 @@
   <hyperlinks>
     <hyperlink ref="C5" r:id="rId1" xr:uid="{7EA46E5E-057B-48C9-8A0D-B56B623EF344}"/>
     <hyperlink ref="C4" r:id="rId2" xr:uid="{8FF96C9D-4D1A-4741-A8FC-C93FF0BAEB17}"/>
-    <hyperlink ref="C12" r:id="rId3" xr:uid="{7720DD14-3F75-4F25-8D70-F6180ED9FB8E}"/>
-    <hyperlink ref="C9" r:id="rId4" xr:uid="{24CE27D2-F11F-4C96-99C0-31B5BD7EA483}"/>
-    <hyperlink ref="C18" r:id="rId5" xr:uid="{09648102-1869-492C-87E8-7FC427C0F56E}"/>
-    <hyperlink ref="C15" r:id="rId6" xr:uid="{2EDD765B-40DE-4D2D-9531-556EBBD3F442}"/>
+    <hyperlink ref="C14" r:id="rId3" xr:uid="{7720DD14-3F75-4F25-8D70-F6180ED9FB8E}"/>
+    <hyperlink ref="C10" r:id="rId4" xr:uid="{24CE27D2-F11F-4C96-99C0-31B5BD7EA483}"/>
+    <hyperlink ref="C20" r:id="rId5" xr:uid="{09648102-1869-492C-87E8-7FC427C0F56E}"/>
+    <hyperlink ref="C17" r:id="rId6" xr:uid="{2EDD765B-40DE-4D2D-9531-556EBBD3F442}"/>
     <hyperlink ref="C2" r:id="rId7" xr:uid="{7787D8AC-7779-42B9-928B-03FC735FB8BD}"/>
-    <hyperlink ref="C8" r:id="rId8" xr:uid="{BA156D29-558F-489F-A67F-2DF63DB9298F}"/>
-    <hyperlink ref="C21" r:id="rId9" xr:uid="{7654C459-BEF7-4D12-A6F9-A473435AB19D}"/>
-    <hyperlink ref="C24" r:id="rId10" xr:uid="{CCF57805-2741-4C93-98B7-D361D0EE1D76}"/>
-    <hyperlink ref="C27" r:id="rId11" xr:uid="{1AD065D4-1978-475F-AE7F-D0045B9251B4}"/>
+    <hyperlink ref="C9" r:id="rId8" xr:uid="{BA156D29-558F-489F-A67F-2DF63DB9298F}"/>
+    <hyperlink ref="C23" r:id="rId9" xr:uid="{7654C459-BEF7-4D12-A6F9-A473435AB19D}"/>
+    <hyperlink ref="C26" r:id="rId10" xr:uid="{CCF57805-2741-4C93-98B7-D361D0EE1D76}"/>
+    <hyperlink ref="C29" r:id="rId11" xr:uid="{1AD065D4-1978-475F-AE7F-D0045B9251B4}"/>
     <hyperlink ref="C3" r:id="rId12" xr:uid="{E821A63E-EBB2-4817-A8B2-87D71FC5D7D5}"/>
+    <hyperlink ref="C6" r:id="rId13" xr:uid="{E5CF6717-1AD5-4E55-A7AC-36F6D056B775}"/>
+    <hyperlink ref="C11" r:id="rId14" xr:uid="{37019985-A607-474E-83E2-936C033D47C7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId13"/>
+  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId15"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDB43275-BEC1-4DF6-B56D-B5F180583A40}">
   <dimension ref="A2:F70"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="2.46484375" customWidth="1"/>
     <col min="2" max="2" width="41.796875" customWidth="1"/>
     <col min="3" max="6" width="20.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" ht="15">
+    <row r="2" spans="1:6" ht="15.4">
       <c r="A2" s="3"/>
       <c r="B2" s="2" t="s">
         <v>100</v>
@@ -2030,7 +2060,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15">
+    <row r="11" spans="1:6" ht="15.4">
       <c r="A11" s="3"/>
       <c r="B11" s="2" t="s">
         <v>106</v>
@@ -2098,7 +2128,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15">
+    <row r="19" spans="1:3" ht="15.4">
       <c r="A19" s="3"/>
       <c r="B19" s="2" t="s">
         <v>107</v>
@@ -2169,7 +2199,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="15">
+    <row r="32" spans="1:3" ht="15.4">
       <c r="A32" s="3"/>
       <c r="B32" s="2" t="s">
         <v>115</v>
@@ -2202,7 +2232,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="15">
+    <row r="38" spans="1:6" ht="15.4">
       <c r="A38" s="3"/>
       <c r="B38" s="2" t="s">
         <v>130</v>
@@ -2211,7 +2241,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="15">
+    <row r="40" spans="1:6" ht="15.4">
       <c r="A40" s="3"/>
       <c r="B40" s="11" t="s">
         <v>54</v>
@@ -2899,14 +2929,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54B06D35-F870-9847-BA9B-1E2F9FFBE611}">
   <dimension ref="A2:C16"/>
-  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="2.46484375" customWidth="1"/>
     <col min="2" max="2" width="24.6640625" customWidth="1"/>
     <col min="3" max="3" width="51" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" ht="15">
+    <row r="2" spans="1:3" ht="15.4">
       <c r="A2" s="3"/>
       <c r="B2" s="2" t="s">
         <v>176</v>
@@ -3001,7 +3031,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CEBDF31-D93E-6148-9E83-2491198D4CE1}">
   <dimension ref="A2:D14"/>
-  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="2.46484375" customWidth="1"/>
     <col min="2" max="2" width="18.46484375" customWidth="1"/>
@@ -3009,7 +3039,7 @@
     <col min="4" max="4" width="34.46484375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:4" ht="15">
+    <row r="2" spans="1:4" ht="15.4">
       <c r="A2" s="3"/>
       <c r="B2" s="2" t="s">
         <v>177</v>
